--- a/untitled folder/HSC_Physics_2nd_Paper_Chapter_06_Geometrical_Optics.xlsx
+++ b/untitled folder/HSC_Physics_2nd_Paper_Chapter_06_Geometrical_Optics.xlsx
@@ -1168,11 +1168,6 @@
           <t>ফার্মার চরম সময় নীতি (Fermat's Principle of Least Time) ব্যাখ্যা করো। এই নীতি প্রয়োগ করে ক্যালকুলাসের সাহায্যে সমতল দর্পণে আলোর প্রতিফলনের দ্বিতীয় সূত্র (আপতন কোণ = প্রতিফলন কোণ, $i = r$) প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>ফার্মার নীতি অনুসারে আলো এক বিন্দু থেকে অন্য বিন্দুতে যাওয়ার সময় এমন পথ অনুসরণ করে যাতে প্রয়োজনীয় সময় ন্যূনতম (বা স্থির) হয়। ধরি সমতল দর্পণ বরাবর $x$-অক্ষ। $A(0, h_1)$ বিন্দু থেকে আলো দর্পণের $P(x, 0)$ বিন্দুতে প্রতিফলিত হয়ে $B(d, h_2)$ বিন্দুতে পৌঁছায়। মোট পথ $s = \sqrt{x^2 + h_1^2} + \sqrt{(d - x)^2 + h_2^2}$। সময় $t = s/c$। চরম সময়ের শর্ত: $\frac{dt}{dx} = 0 \implies \frac{1}{c}\left[\frac{x}{\sqrt{x^2 + h_1^2}} - \frac{d - x}{\sqrt{(d - x)^2 + h_2^2}}\right] = 0$। জ্যামিতি থেকে $\frac{x}{\sqrt{x^2 + h_1^2}} = \sin i$ এবং $\frac{d - x}{\sqrt{(d - x)^2 + h_2^2}} = \sin r$। ফলে $\sin i - \sin r = 0 \implies \sin i = \sin r \implies i = r$।</t>
@@ -1218,11 +1213,6 @@
           <t>উপাক্ষীয় রশ্মির (paraxial rays) ক্ষেত্রে কার্তেসীয় চিহ্নের প্রথা অনুসারে অবতল ও উত্তল উভয় গোলীয় দর্পণের জন্য সাধারণ সমীকরণ $\frac{1}{v} + \frac{1}{u} = \frac{1}{f} = \frac{2}{R}$ প্রতিপাদন করো। দর্পণের ফোকাস দূরত্ব কেন চারপাশের মাধ্যমের প্রতিসরাঙ্কের ওপর নির্ভর করে না?</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>অবতল দর্পণে বক্রতার কেন্দ্র $C$ এবং প্রধান ফোকাস $F$। প্রধান অক্ষের ওপর $O$ বিন্দু থেকে নির্গত উপাক্ষীয় রশ্মি দর্পণের $M$ বিন্দুতে আপতিত হয়ে $I$ বিন্দুতে মিলিত হয়। কোণগুলো ক্ষুদ্র বিবেচনা করে স্পর্শক সমান কোণ লিখলে: $\alpha \approx \frac{MP}{u}$, $\beta \approx \frac{MP}{R}$, $\gamma \approx \frac{MP}{v}$। ত্রিভুজের বহিস্থ কোণের উপপাদ্য থেকে: $\beta = \alpha + \theta$ এবং $\gamma = \beta + \theta \implies \alpha + \gamma = 2\beta$। মান বসালে: $\frac{MP}{u} + \frac{MP}{v} = 2\frac{MP}{R} \implies \frac{1}{u} + \frac{1}{v} = \frac{2}{R} = \frac{1}{f}$। যেহেতু আলোর প্রতিফলনে স্নেলের প্রতিসরণ সূত্রের প্রয়োজন হয় না এবং প্রতিফলন সূত্র ($i=r$) মাধ্যমের আলোর বেগের ওপর স্বাধীন, তাই দর্পণকে পানিতে নিমজ্জিত করলেও এর ফোকাস দূরত্ব অপরিবর্তিত থাকে।</t>
@@ -1268,11 +1258,6 @@
           <t>একটি গোলীয় দর্পণে ক্ষুদ্র রৈখিক বস্তুর অনুপ্রস্থ বা রৈখিক বিবর্ধন $m = -\frac{v}{u}$। প্রধান অক্ষ বরাবর স্থাপিত একটি অতি ক্ষুদ্র দৈর্ঘ্য $\Delta u$-এর বস্তুর অনুদৈর্ঘ্য বিবর্ধন (longitudinal magnification, $m_L$) নির্ণয় করো এবং প্রমাণ করো যে $m_L = -m^2$।</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>দর্পণের সাধারণ সমীকরণ: $\frac{1}{u} + \frac{1}{v} = \frac{1}{f}$। $u$-এর সাপেক্ষে উভয়পাশে ব্যবকলন করে (যেহেতু ফোকাস দূরত্ব $f$ ধ্রুবক): $-\frac{1}{u^2} - \frac{1}{v^2}\frac{dv}{du} = 0 \implies \frac{1}{v^2}\frac{dv}{du} = -\frac{1}{u^2} \implies \frac{dv}{du} = -\frac{v^2}{u^2}$। অনুদৈর্ঘ্য বিবর্ধন হলো অক্ষ বরাবর প্রতিবিম্বের দৈর্ঘ্য ও বস্তুর দৈর্ঘ্যের অনুপাত: $m_L \equiv \frac{\Delta v}{\Delta u} \approx \frac{dv}{du} = -\left(\frac{v}{u}\right)^2$। কিন্তু অনুপ্রস্থ বিবর্ধন $m = -\frac{v}{u}$। অতএব $m_L = -m^2$। ঋণাত্মক চিহ্ন নির্দেশ করে যে অক্ষীয় প্রতিবিম্বটি সর্বদা উল্টানো হয় এবং বর্গের কারণে অনুদৈর্ঘ্য বিবর্ধন সর্বদা ঋণাত্মক থাকে।</t>
@@ -1318,11 +1303,6 @@
           <t>$f$ ফোকাস দূরত্বের একটি অবতল দর্পণের প্রধান অক্ষ বরাবর $u$ দূরত্বে অবস্থিত একটি বস্তু $v_o$ ধ্রুব দ্রুতিতে দর্পণের দিকে অগ্রসর হচ্ছে। প্রতিবিম্বের তাৎক্ষণিক বেগ $v_i$-এর রাশিমালা $u, f$ ও $v_o$-এর মাধ্যমে নির্ণয় করো। বস্তু যখন ফোকাসের দিকে আসে তখন প্রতিবিম্বের বেগ কীভাবে পরিবর্তিত হয়?</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>দর্পণের সমীকরণ ব্যবকলন করে আমরা জানি: $\frac{dv}{dt} = -\frac{v^2}{u^2}\frac{du}{dt}$। দর্পণের সমীকরণ থেকে: $\frac{1}{v} = \frac{1}{f} - \frac{1}{u} = \frac{u - f}{u f} \implies \frac{v}{u} = \frac{f}{u - f}$। মান বসালে পাই: $v_i = -\left(\frac{f}{u - f}\right)^2 v_o$। ঋণাত্মক চিহ্ন নির্দেশ করে যে বস্তু যেদিকে চলে, প্রতিবিম্ব তার বিপরীত অভিমুখে গতিশীল হয়। যখন বস্তুটি অসীম থেকে বক্রতার কেন্দ্রের দিকে আসে, প্রতিবিম্বের বেগ কম থাকে ($v_i &lt; v_o$)। বক্রতার কেন্দ্রে ($u = 2f$) উভয় বেগ সমান হয় ($v_i = v_o$)। এরপর বস্তু যখন ফোকাসের কাছাকাছি যায় ($u \to f$), তখন হর শূন্যের কাছাকাছি পৌঁছায় এবং প্রতিবিম্বের বেগ অসীমের দিকে ধাবিত হয়।</t>
@@ -1368,11 +1348,6 @@
           <t>বৃহৎ উন্মেষের গোলীয় দর্পণে প্রান্তিক রশ্মি (marginal rays) ও উপাক্ষীয় রশ্মির (paraxial rays) ফোকাস বিন্দুর বিচ্যুতির ফলে সৃষ্ট গোলীয় বিপথন (Spherical Aberration) ব্যাখ্যা করো। আধুনিক জ্যোতির্বৈজ্ঞানিক দূরবীক্ষণে গোলীয় দর্পণের বদলে অধিবৃত্তীয় (Parabolic) দর্পণ কেন ব্যবহার করা হয়?</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>গোলীয় দর্পণে প্রধান অক্ষের সমান্তরাল রশ্মির জন্য ফোকাস দূরত্ব হয় $F_P = R - \frac{R}{2\cos \theta}$। উপাক্ষীয় রশ্মির জন্য $\theta \to 0 \implies \cos \theta \approx 1$, ফলে $f = R/2$। কিন্তু প্রান্তিক রশ্মির জন্য $\theta$ বড় হওয়ায় $\cos \theta &lt; 1$, ফলে ফোকাস মেরুর সন্নিকটে সরে আসে। এর ফলে সমান্তরাল রশ্মিগুলো একটি বিন্দুতে মিলিত না হয়ে একটি বৃত্তাকার অস্পষ্ট প্যাচ (circle of least confusion) তৈরি করে। অধিবৃত্তের (Parabola) গাণিতিক বৈশিষ্ট্য হলো: এর অক্ষের সমান্তরাল যে কোনো রশ্মি প্রতিফলিত হয়ে সর্বদা এর একমাত্র নাভি বা ফোকাস বিন্দুতে নিখুঁতভাবে মিলিত হয়, কোনো প্রান্তীয় বিচ্যুতি ছাড়াই। ফলে হাবল বা জেমস ওয়েব টেলিস্কোপে নিখুঁত স্পষ্ট প্রতিবিম্বের জন্য অধিবৃত্তীয় প্রতিফলক ব্যবহৃত হয়।</t>
@@ -1418,11 +1393,6 @@
           <t>$\theta$ কোণে আনত দুটি সমতল দর্পণের মধ্যবর্তী স্থানে একটি বিন্দু বস্তু রাখা হলো। গঠিত প্রতিবিম্বের সংখ্যার ($n$) পূর্ণাঙ্গ নিয়মটি $m = \frac{360^\circ}{\theta}$-এর জোড় ও বিজোড় মানের শর্তসাপেক্ষে ব্যাখ্যা করো। দর্পণদ্বয় সমান্তরাল হলে ($\theta = 0$) প্রতিবিম্বের সংখ্যা কত?</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>দর্পণদ্বয়ের ছেদবিন্দুকে কেন্দ্র করে একটি বৃত্তের পরিধির ওপর সমস্ত প্রতিবিম্ব গঠিত হয়। $m = \frac{360^\circ}{\theta}$ গণনা করা হয়। ১) $m$ জোড় সংখ্যা হলে: বস্তুটি যেকোনো অবস্থানেই থাকুক না কেন, দুটি প্রতিবিম্ব হুবহু একই বিন্দুতে সমাপতিত (overlap) হয়। ফলে কার্যকর প্রতিবিম্ব সংখ্যা সর্বদা $n = m - 1$। যেমন $\theta = 90^\circ$ হলে $m = 4$, ফলে $n = 3$। ২) $m$ বিজোড় সংখ্যা হলে: ক) বস্তুটি কোণটির সমদ্বিখণ্ডকের ওপর প্রতিসমভাবে থাকলে $n = m - 1$, খ) অপ্রতিসমভাবে থাকলে কোনো ওভারল্যাপ হয় না, ফলে $n = m$। ৩) সমান্তরাল দর্পণে ($\theta = 0^\circ$): $m = \frac{360^\circ}{0} \to \infty$, ফলে বারবার প্রতিফলনের মাধ্যমে অসীম সংখ্যক প্রতিবিম্ব গঠিত হয়।</t>
@@ -1468,11 +1438,6 @@
           <t>মোটরযানের চালকের পেছনের দৃশ্য দেখার দর্পণ (Rear-view mirror) হিসেবে সমতল বা অবতল দর্পণের পরিবর্তে উত্তল দর্পণ ব্যবহার করার কারণ কী? দৃষ্টি ক্ষেত্রের (Field of view) জ্যামিতিক চিত্রের সাহায্যে ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>উত্তল দর্পণের ক্ষেত্রে ফোকাস দূরত্ব ধনাত্মক ($f &gt; 0$) এবং বস্তু সর্বদা সামনে থাকে ($u &lt; 0$)। সমীকরণ $\frac{1}{v} = \frac{1}{f} - \frac{1}{u} = \frac{1}{f} + \frac{1}{|u|} &gt; 0$। ফলে প্রতিবিম্ব সর্বদা দর্পণের পেছনে গঠিত হয় এবং বিবর্ধন $m = -\frac{v}{u} = \frac{v}{|u|} &lt; 1$। অর্থাৎ যেকোনো দূরত্বে থাকা বস্তুর জন্য এটি সর্বদা সোজা ও ছোট অসদ প্রতিবিম্ব গঠন করে। দ্বিতীয়ত, প্রতিফলক পৃষ্ঠটি বহির্মুখী উত্তল হওয়ায় চালকের চোখের সাপেক্ষে প্রতিফলিত প্রান্তিক রশ্মিগুলো একটি বিশাল কোণ জুড়ে চারদিকে বিস্তৃত হয়। ফলে চালক পেছনের একটি সুবিশাল এলাকার সম্পূর্ণ ট্রাফিককে একটি ছোট দর্পণের ভেতর স্পষ্ট দেখতে পায়।</t>
@@ -1518,11 +1483,6 @@
           <t>$f$ ফোকাস দূরত্বের একটি অবতল দর্পণে একটি বাস্তব বস্তুর বাস্তব প্রতিবিম্ব গঠিত হয়েছে। বস্তু এবং তার বাস্তব প্রতিবিম্বের মধ্যবর্তী দূরত্বের সর্বনিম্ন মান কত এবং কোন অবস্থানে এটি ঘটে?</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>অবতল দর্পণে বাস্তব বস্তুর বাস্তব প্রতিবিম্ব গঠিত হয় যখন বস্তুটি ফোকাসের বাইরে থাকে ($u \ge f$)। বস্তু ও প্রতিবিম্বের মধ্যবর্তী দূরত্ব $D = |u - v|$। দর্পণের সমীকরণ থেকে: $v = \frac{u f}{u - f}$। দূরত্ব $D(u) = u - \frac{u f}{u - f} = \frac{u^2 - 2 u f}{u - f}$। দূরত্বের চরম মান নির্ণয়ের জন্য $\frac{dD}{du} = 0 \implies \frac{(2u - 2f)(u - f) - (u^2 - 2uf)(1)}{(u - f)^2} = 0 \implies 2u^2 - 4uf + 2f^2 - u^2 + 2uf = 0 \implies u^2 - 2uf + 2f^2 \dots$ সরাসরি দেখা যায় যখন $u = 2f$ (বক্রতার কেন্দ্র), তখন $v = \frac{2f \cdot f}{2f - f} = 2f$। ফলে বস্তু ও প্রতিবিম্ব হুবহু একই বিন্দুতে অবস্থান করে এবং তাদের মধ্যবর্তী দূরত্ব $D = |2f - 2f| = 0$।</t>
@@ -1568,11 +1528,6 @@
           <t>একটি সমতল দর্পণে একটি স্থির আলোক রশ্মি আপতিত হচ্ছে। দর্পণটিকে আপতন তলে এর স্পর্শক অক্ষের সাপেক্ষে $\theta$ কোণে ঘুরিয়ে দিলে প্রতিফলিত রশ্মি কত কোণে ঘুরে যাবে? জ্যামিতিকভাবে প্রমাণ করো।</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>ধরি প্রাথমিক অবস্থায় দর্পণের অভিলম্ব $N_1$ এবং আপতন কোণ $i$। ফলে আপতিত রশ্মি ও প্রতিফলিত রশ্মির মধ্যবর্তী কোণ $\angle A O R_1 = 2i$। দর্পণটিকে $\theta$ কোণে ঘোরালে এর ওপর অঙ্কিত অভিলম্বও $\theta$ কোণে ঘুরে নতুন অবস্থান $N_2$-তে যায়। যেহেতু আপতিত রশ্মি স্থির, তাই নতুন আপতন কোণ হয় $i' = i + \theta$। প্রতিফলনের দ্বিতীয় সূত্রানুযায়ী নতুন প্রতিফলন কোণও হবে $r' = i + \theta$। অতএব আপতিত রশ্মি ও নতুন প্রতিফলিত রশ্মির মধ্যবর্তী মোট কোণ $\angle A O R_2 = 2(i + \theta) = 2i + 2\theta$। ফলে প্রতিফলিত রশ্মির কৌণিক ঘূর্ণন $\delta = \angle A O R_2 - \angle A O R_1 = (2i + 2\theta) - 2i = 2\theta$। অর্থাৎ দর্পণ যে কোণে ঘোরে, প্রতিফলিত রশ্মি ঠিক তার দ্বিগুণ কোণে ঘুরে যায়।</t>
@@ -1618,11 +1573,6 @@
           <t>ভেতরের পৃষ্ঠ প্রতিফলক বিশিষ্ট একটি ঘনকাকৃতি ঘরের মেঝের ঠিক কেন্দ্রে একটি বিন্দু আলোক উৎস রাখা আছে। এই কক্ষের দেয়াল ও ছাদ থেকে বারবার প্রতিফলনের পর গঠিত প্রতিবিম্বগুলোর জ্যামিতিক বিন্যাস কেমন হবে?</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>সমতল দর্পণে প্রতিবিম্ব গঠনের ক্ষেত্রে দর্পণটিকে একটি প্রতিসাম্য প্রতিফলক সমতল বিবেচনা করা যায়। ঘনকটির ৬টি দেয়াল ৩ জোড়া সমান্তরাল দর্পণ গঠন করে ($x, y, z$ অক্ষে)। একটি সমান্তরাল দর্পণ জোড়া এক-মাত্রিক অসীম শৃঙ্খল প্রতিবিম্ব তৈরি করে। তিনটি পরস্পর লম্ব অক্ষ বরাবর সমান্তরাল দর্পণ যুগল স্থান জুড়ে একটি পূর্ণ ত্রিমাত্রিক পর্যায়বৃত্ত ঘনকাকৃতি স্ফটিক ল্যাটিস (cubic crystal lattice) তৈরি করে। ঘরের ভেতরে দাঁড়ানো একজন পর্যবেক্ষক নিজেকে একটি অন্তহীন ত্রিমাত্রিক মহাবিশ্বে অসীম সংখ্যক আলোকময় ঘরের অসীম শৃঙ্খলের কেন্দ্রে দেখতে পাবেন।</t>
@@ -1668,11 +1618,6 @@
           <t>আপতিত রশ্মির একক ভেক্টর $\hat{s}_1$, প্রতিসরিত রশ্মির একক ভেক্টর $\hat{s}_2$, বিভেদতলের বহির্মুখী অভিলম্ব একক ভেক্টর $\hat{n}$ এবং মাধ্যমদ্বয়ের প্রতিসরাঙ্ক $n_1$ ও $n_2$ হলে স্নেলের সূত্রের পূর্ণাঙ্গ ভেক্টর রূপটি প্রতিষ্ঠা করো।</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>স্নেলের চিরায়ত রূপ $n_1 \sin i = n_2 \sin r$। ভেক্টর গুণনের সংজ্ঞামতে $|\hat{s}_1 \times \hat{n}| = \sin i$ এবং $|\hat{s}_2 \times \hat{n}| = \sin r$। যেহেতু আপতিত রশ্মি, প্রতিসরিত রশ্মি এবং অভিলম্ব একই সমতলে থাকে, তাই $\hat{s}_1 \times \hat{n}$ এবং $\hat{s}_2 \times \hat{n}$ ভেক্টর দুটি অভিন্ন সমতলের লম্ব একক ভেক্টর নির্দেশ করে। অতএব ভেক্টর আকারে: $n_1 (\hat{s}_1 \times \hat{n}) = n_2 (\hat{s}_2 \times \hat{n})$। রে-ট্রেসিং এবং থ্রিডি কম্পিউটার গ্রাফিক্সে কম্পিউটারকে প্রতিসরণ গণনা করাতে এই ভেক্টর রূপটি ব্যবহৃত হয়।</t>
@@ -1718,11 +1663,6 @@
           <t>$t$ পুরুত্ব এবং $\mu$ প্রতিসরাঙ্কের একটি কাঁচের সমান্তরাল স্ল্যাবের ওপর $i$ আপতন কোণে আলো আপতিত হলো। স্ল্যাবটি অতিক্রমকালে নির্গত সমান্তরাল রশ্মির পার্শ্ব সরণ (Lateral Displacement, $d$)-এর রাশিমালা প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>স্ল্যাবের প্রথম পৃষ্ঠে আপতন কোণ $i$ ও প্রতিসরণ কোণ $r$। দ্বিতীয় পৃষ্ঠে আপতন কোণ $r$ হওয়ায় নির্গমন কোণ পুনরায় $i$ হয়, অর্থাৎ নির্গত রশ্মি আপতিত রশ্মির সমান্তরাল থাকে। পার্শ্ব সরণ হলো আপতিত রশ্মির বর্ধিতাংশ এবং নির্গত রশ্মির মধ্যবর্তী লম্ব দূরত্ব $d$। কাঁচের ভেতরের পথ $A B = \frac{t}{\cos r}$। পথচ্যুতি কোণ $(i - r)$। জ্যামিতিক সমকোণী ত্রিভুজ থেকে পার্শ্ব সরণ $d = A B \sin(i - r) = \frac{t}{\cos r}\sin(i - r) = t \frac{\sin i \cos r - \cos i \sin r}{\cos r} = t \sin i(1 - \tan r \cot i)$। স্নেলের সূত্রে $\sin r = \frac{\sin i}{\mu}$ বসালে পাই: $d = t \sin i \left[1 - \frac{\cos i}{\sqrt{\mu^2 - \sin^2 i}}\right]$।</t>
@@ -1768,11 +1708,6 @@
           <t>একটি পাত্রে যথাক্রমে $t_1, t_2, \dots, t_n$ পুরুত্বের এবং $\mu_1, \mu_2, \dots, \mu_n$ প্রতিসরাঙ্কের একাধিক অমিলনশীল তরল স্তর সমান্তরালে সাজানো আছে। পাত্রের তলদেশের আপাত গভীরতা $d_{\text{apparent}}$ এবং উল্লম্ব আপাত সরণ $\Delta y$-এর সাধারণ সূত্রটি লেখো।</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>ঘন মাধ্যম থেকে হালকা মাধ্যমে লম্বভাবে আলো দেখলে প্রতিসরণের কারণে প্রতিটি স্তর তার নিজস্ব উপাদানকে $\Delta y_k = t_k(1 - 1/\mu_k)$ পরিমাণ উপরে তুলে দেখায়। ফলে প্রতিটি স্তরের কার্যকর আপাত বেধ হয় $t'_k = \frac{t_k}{\mu_k}$। যেহেতু স্তরগুলো পরস্পরের ওপর সমান্তরালে স্তরীভূত, তাই সমগ্র ব্যবস্থার লব্ধি আপাত গভীরতা হলো পৃথক পৃথক আপাত গভীরতাগুলোর সাধারণ যোগফল: $d_{\text{apparent}} = \frac{t_1}{\mu_1} + \frac{t_2}{\mu_2} + \dots + \frac{t_n}{\mu_n} = \sum_{k=1}^n \frac{t_k}{\mu_k}$। মোট আপাত সরণ $\Delta y = \text{প্রকৃত গভীরতা} - \text{আপাত গভীরতা} = \sum t_k - \sum \frac{t_k}{\mu_k} = \sum t_k \left(1 - \frac{1}{\mu_k}\right)$।</t>
@@ -1818,11 +1753,6 @@
           <t>পানির প্রতিসরাঙ্ক $\mu = 4/3$। পানির নিচে $h$ গভীরতায় অবস্থিত একটি বিন্দু আলোক উৎস থেকে নির্গত সমস্ত আলো পানির পৃষ্ঠের ওপর একটি বৃত্তাকার ক্ষেত্রফল দিয়ে বাতাসে বেরিয়ে আসে। পূর্ণ অভ্যন্তরীণ প্রতিফলনের সাহায্যে এই আলোকোজ্জ্বল বৃত্তের ব্যাসার্ধ $R$ এবং ক্ষেত্রফল $A$-এর রাশিমালা প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>উৎস থেকে যে সমস্ত আলোক রশ্মি পানির পৃষ্ঠে সংকট কোণ $\theta_c$-এর চেয়ে কম কোণে আপতিত হয় কেবল তারাই প্রতিসরিত হয়ে বাতাসে প্রবেশ করতে পারে। যে রশ্মিগুলো ঠিক সংকট কোণে আপতিত হয় সেগুলো পৃষ্ঠ ঘেঁষে ৯০ ডিগ্রি কোণে নির্গত হয়। এর বাইরের সমস্ত রশ্মি পূর্ণ অভ্যন্তরীণ প্রতিফলনে পুনরায় পানির নিচে ফিরে আসে। ফলে পানির পৃষ্ঠে একটি বৃত্তাকার আলোকীয় জানালা তৈরি হয় যার ব্যাসার্ধ $R$ এবং কেন্দ্রে কোণ $\theta_c$। জ্যামিতি থেকে $\tan \theta_c = \frac{R}{h} \implies R = h \tan \theta_c$। আবার সংকট কোণের সূত্রে $\sin \theta_c = \frac{1}{\mu} \implies \cos \theta_c = \sqrt{1 - 1/\mu^2} = \frac{\sqrt{\mu^2 - 1}}{\mu}$। অতএব $\tan \theta_c = \frac{\sin \theta_c}{\cos \theta_c} = \frac{1}{\sqrt{\mu^2 - 1}}$। মান বসালে ব্যাসার্ধ $R = \frac{h}{\sqrt{\mu^2 - 1}}$ এবং ক্ষেত্রফল $A = \pi R^2 = \frac{\pi h^2}{\mu^2 - 1}$।</t>
@@ -1868,11 +1798,6 @@
           <t>একটি অপটিক্যাল ফাইবারের কোরের (core) প্রতিসরাঙ্ক $n_1$ এবং ক্ল্যাডিংয়ের (cladding) প্রতিসরাঙ্ক $n_2$ ($n_1 &gt; n_2$)। ফাইবারটির মুখে সর্বাধিক যে আপতন কোণে আলো প্রবেশ করালে তা পূর্ণ অভ্যন্তরীণ প্রতিফলনে ফাইবারের ভেতর দিয়ে পথ অতিক্রম করে সেই গ্রহণযোগ্য কোণ (Acceptance Angle, $\theta_a$) এবং নিউমেরিক্যাল অ্যাপারচার ($NA$)-এর সমীকরণ প্রতিষ্ঠা করো।</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>ফাইবারের সমতল মুখে বাতাস থেকে আলো $\theta_a$ কোণে প্রবেশ করে $r$ কোণে প্রতিসরিত হয়: $\sin \theta_a = n_1 \sin r$। এই রশ্মিটি যখন কোরের দেয়াল ও ক্ল্যাডিংয়ের ইন্টারফেসে আঘাত হানে, তখন সেখানে আপতন কোণ হয় $\phi = 90^\circ - r$। পূর্ণ অভ্যন্তরীণ প্রতিফলনের শর্ত হলো $\phi \ge \theta_c \implies \sin(90^\circ - r) \ge \sin \theta_c \implies \cos r \ge \frac{n_2}{n_1}$। ত্রিকোণমিতি থেকে $\sin r = \sqrt{1 - \cos^2 r} \le \sqrt{1 - (n_2/n_1)^2} = \frac{\sqrt{n_1^2 - n_2^2}}{n_1}$। এই মান প্রথম সমীকরণে বসালে পাই: $\sin \theta_a = n_1 \sin r \le n_1 \frac{\sqrt{n_1^2 - n_2^2}}{n_1} = \sqrt{n_1^2 - n_2^2}$। অতএব নিউমেরিক্যাল অ্যাপারচার $NA \equiv \sin \theta_a = \sqrt{n_1^2 - n_2^2}$।</t>
@@ -1918,11 +1843,6 @@
           <t>উত্তপ্ত মরুভূমিতে মরীচিকা (Mirage) সৃষ্টির পেছনে বায়ুমণ্ডলের তাপমাত্রা বৃদ্ধির সাথে প্রতিসরাঙ্কের পরিবর্তন এবং আলোর বক্ররেখা বরাবর পূর্ণ অভ্যন্তরীণ প্রতিফলনের ভূমিকা সমাকলন দৃষ্টিকোণ থেকে ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>তপ্ত বালুর সংস্পর্শে থাকা নিচের বাতাসের স্তরগুলো অত্যন্ত উত্তপ্ত ও প্রসারিত থাকে, ফলে তাদের ঘনত্ব সর্বনিম্ন হয়। উপরে উঠলে বাতাস তুলনামূলক ঠান্ডা ও ঘন হতে থাকে। ফলে উচ্চতা $y$-এর সাথে বায়ুর প্রতিসরাঙ্ক বৃদ্ধি পায়: $\frac{dn}{dy} &gt; 0$। দূরের কোনো গাছের শীর্ষ থেকে আগত আলো যখন নিচের দিকে ধাবিত হয়, তখন এটি অবিরাম ঘন মাধ্যম থেকে হালকা মাধ্যমে প্রবেশ করে। ফলে আলোর পথ প্রতিটি স্তরে অভিলম্ব থেকে দূরে বেঁকে একটি অধোমুখী প্যারাবোলিক বক্ররেখা তৈরি করে। একপর্যায়ে আপতন কোণ স্থানীয় সংকট কোণকে অতিক্রম করলে আলোকের পূর্ণ অভ্যন্তরীণ প্রতিফলন ঘটে এবং রশ্মিটি ঊর্ধ্বমুখী বাঁক নিয়ে পথিকের চোখে প্রবেশ করে। পথিকের মস্তিষ্ক মনে করে আলো সরলরেখায় নিচ থেকে আসছে, ফলে সে গাছের নিচে বালুর ওপর আকাশের একটি কম্পমান উল্টানো প্রতিবিম্ব দেখে যাকে দূর থেকে পানির পুকুর বলে মনে হয়।</t>
@@ -1968,11 +1888,6 @@
           <t>সমদ্বিবাহু সমকোণী কাঁচের প্রিজমকে ($\mu = 1.5$) পোরা প্রিজম বলে। আলোর পূর্ণ অভ্যন্তরীণ প্রতিফলনকে কাজে লাগিয়ে এই প্রিজম কীভাবে (ক) আলোকে ঠিক $90^\circ$ কোণে বিচ্যুত করে এবং (খ) আলোকে ঠিক $180^\circ$ কোণে ঘুরিয়ে প্রতিবিম্বকে কোনো আলোর তীব্রতা না কমিয়ে উল্টে দেয়?</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>কাঁচের সংকট কোণ $\sin \theta_c = \frac{1}{1.5} \approx 0.667 \implies \theta_c \approx 41.8^\circ$। পোরা প্রিজমের কোণগুলো $45^\circ - 90^\circ - 45^\circ$। ১) $90^\circ$ বিচ্যুতির ক্ষেত্রে: আলো একটি সমকোণী বাহুর ওপর লম্বভাবে প্রবেশ করে অতিভুজ পৃষ্ঠে $45^\circ$ কোণে আপতিত হয়। যেহেতু $45^\circ &gt; 41.8^\circ$, তাই কোনো প্রতিসরণ হয় না, শতভাগ আলো পূর্ণ অভ্যন্তরীণ প্রতিফলনে $90^\circ$ কোণে অন্য বাহু দিয়ে বেরিয়ে যায়। ২) $180^\circ$ বিচ্যুতির ক্ষেত্রে: আলো অতিভুজ পৃষ্ঠে লম্বভাবে ঢুকে দুটি সমকোণী বাহুতে পরপর দুবার $45^\circ$ কোণে পূর্ণ অভ্যন্তরীণ প্রতিফলিত হয়ে মোট $90^\circ + 90^\circ = 180^\circ$ ঘুরে ফিরে আসে। সাধারণ দর্পণে পারদ প্রলেপ ৮-১০% আলো শোষণ করে, কিন্তু পোরা প্রিজমে কোনো রূপালী প্রলেপ ছাড়াই শতভাগ আলো প্রতিফলিত হয়।</t>
@@ -2018,11 +1933,6 @@
           <t>পানির ভেতরে অবস্থিত একটি $R$ ব্যাসার্ধের গোলাকার বায়ুর বুদবুদে একটি সমান্তরাল রশ্মি আপতিত হলো। বুদবুদটি অপসারী লেন্সের ন্যায় আচরণ করে কেন? অক্ষীয় সমান্তরাল আলোকরশ্মির কত অংশ বুদবুদের ভেতর প্রবেশ করতে পারে?</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>পানির প্রতিসরাঙ্ক $\mu = 4/3$ এবং বায়ুর প্রতিসরাঙ্ক $1$। গোলীয় তলের প্রতিসরণ সমীকরণ $\frac{\mu_2}{v} - \frac{\mu_1}{u} = \frac{\mu_2 - \mu_1}{R}$। এখানে $\mu_1 = 4/3$ (ঘন) এবং $\mu_2 = 1$ (হালকা)। সমতল রশ্মির জন্য $u = -\infty$। প্রথম তলে $\frac{1}{v_1} = \frac{1 - 4/3}{R} = -\frac{1}{3R} \implies v_1 = -3R$। অর্থাৎ প্রতিবিম্বটি আপতন তলের পেছনে অসদ হিসেবে তৈরি হয় এবং রশ্মিগুলো অপসারিত হয়। দ্বিতীয়ত, কেন্দ্র থেকে $b$ ইমপ্যাক্ট প্যারামিটারে আপতিত রশ্মির জন্য আপতন কোণ $\sin i = b/R$। পানি থেকে বায়ুর সংকট কোণ $\sin \theta_c = 1/\mu = 3/4$। যদি $b/R &gt; 3/4 \implies b &gt; 0.75 R$ হয়, তবে আলো বুদবুদের ভেতরে ঢুকতেই পারে না, বাইরে থেকেই পূর্ণ প্রতিফলিত হয়ে চকচক করে।</t>
@@ -2068,11 +1978,6 @@
           <t>পূর্ণ অভ্যন্তরীণ প্রতিফলনের (TIR) সময় আলো হালকা মাধ্যমে প্রবেশ না করে শতভাগ প্রতিফলিত হলেও ম্যাক্সওয়েলের তড়িচ্চৌম্বক সমীকরণ দেখায় যে হালকা মাধ্যমে একটি ক্ষয়িষ্ণু ইভানেসেন্ট তরঙ্গ (Evanescent Wave) উপস্থিত থাকে। এই তরঙ্গের শক্তি প্রবাহ কেন শূন্য এবং ফ্রাস্ট্রেটেড টিআইআর (FTIR) কীভাবে কোয়ান্টাম টানেলিংয়ের সমতুল্য?</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>ম্যাক্সওয়েলের বাউন্ডারি শর্তানুযায়ী বিভেদতলে তড়িৎ ও চৌম্বক ক্ষেত্রের স্পর্শক উপাংশ অবিচ্ছিন্ন থাকতে হয়। ফলে পূর্ণ অভ্যন্তরীণ প্রতিফলনের সময় হালকা মাধ্যমের উপরিভাগে কয়েকশ ন্যানোমিটার গভীরতা পর্যন্ত একটি ক্ষয়িষ্ণু ক্ষেত্র প্রবেশ করে যার বিস্তার $E(z) = E_0 e^{-z / d_p}$। এর তরঙ্গ ভেক্টর জটিল হওয়ায় আলো হালকা মাধ্যমের দিকে কোনো নিট শক্তি পরিবহন করে না ($S_z = 0$)। কিন্তু যদি এই ক্ষয়িষ্ণু ক্ষেত্রের সীমানার ভেতর (দূরত্ব $&lt; \lambda$) দ্বিতীয় আরেকটি উচ্চ প্রতিসরাঙ্কের কাঁচের প্রিজম চেপে ধরা হয়, তবে আলো ঐ শূন্যস্থান কোয়ান্টাম কণার ন্যায় 'টানেলিং' করে দ্বিতীয় প্রিজমে প্রবেশ করে একটি ট্রান্সমিটেড রশ্মি তৈরি করে। একে ফ্রাস্ট্রেটেড টোটাল ইন্টারনাল রিফ্লেকশন (FTIR) বলে যা আধুনিক অপটিক্যাল টাচস্ক্রিন ও এটিআর স্পেকট্রোস্কোপিতে ব্যবহৃত হয়।</t>
@@ -2118,11 +2023,6 @@
           <t>হীরকের প্রতিসরাঙ্ক ($\mu \approx 2.42$) কাঁচের ($\mu \approx 1.5$) তুলনায় অনেক বেশি হওয়ায় হীরকের সংকট কোণ কত হয়? দক্ষ রত্নকাররা হীরককে এমন বিশেষ জ্যামিতিক কোণে কর্তন করেন কেন যাতে এর ভেতরে 'আগুনের ঝিলিক' (brilliance and fire) দেখা যায়?</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>হীরকের অতিউচ্চ প্রতিসরাঙ্কের কারণে সংকট কোণ মাত্র ২৪.৪ ডিগ্রি। একটি কাঁচের ক্ষেত্রে সংকট কোণ ৪২ ডিগ্রি হওয়ায় অধিকাংশ আলো প্রথম আঘাতেই বাইরে বেরিয়ে যায়। কিন্তু হীরককে যখন বিখ্যাত 'ব্রিলিয়ান্ট কাট' (Brilliant Cut) জ্যামিতিতে কাটা হয়, তখন হীরকের শীর্ষফলক দিয়ে একবার প্রবেশ করা আলো নিচের তলগুলোতে সর্বদা ২৪.৪ ডিগ্রির চেয়ে বেশি কোণে আপতিত হতে বাধ্য হয়। ফলে আলো নিচে দিয়ে বের হতে না পেরে বারবার ভেতরে পূর্ণ প্রতিফলিত হতে থাকে। সবশেষে রশ্মিগুলো একত্রিত হয়ে কেবল ওপরের সমতল মুখগুলো দিয়ে তীব্র কেন্দ্রীভূত আলোকচ্ছটা হয়ে নির্গত হয়। তদুপরি হীরকের উচ্চ বিচ্ছুরণ ক্ষমতার কারণে বিভিন্ন বর্ণের আলো ভিন্ন কোণে ভেঙে গিয়ে চোখ ধাঁধানো রামধনু রঙের ঝিলিক তৈরি করে।</t>
@@ -2168,11 +2068,6 @@
           <t>$A$ প্রতিসারক কোণের একটি প্রিজমে প্রথম পৃষ্ঠে আপতন কোণ $i_1$, প্রতিসরণ কোণ $r_1$, দ্বিতীয় পৃষ্ঠে আপতন কোণ $r_2$ এবং নির্গমন কোণ $i_2$। জ্যামিতিক প্রমাণের সাহায্যে দেখাও যে (ক) $r_1 + r_2 = A$, এবং (খ) মোট বিচ্যুতি কোণ $\delta = i_1 + i_2 - A$।</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>প্রিজমের প্রতিসারক তলদ্বয়ের মধ্যবর্তী কোণ $A$। প্রথম তলে আপতিত রশ্মি $i_1$ কোণে ঢুকে $r_1$ কোণে প্রতিসরিত হয়। এর বিচ্যুতি $\delta_1 = i_1 - r_1$। দ্বিতীয় তলে আলো $r_2$ কোণে আপতিত হয়ে $i_2$ কোণে নির্গত হয়। এর বিচ্যুতি $\delta_2 = i_2 - r_2$। মোট বিচ্যুতি $\delta = \delta_1 + \delta_2 = (i_1 - r_1) + (i_2 - r_2) = (i_1 + i_2) - (r_1 + r_2)$। প্রিজমের অভ্যন্তরীণ ত্রিভুজ $QNR$-এ তিনটি কোণের সমষ্টি $180^\circ \implies r_1 + r_2 + \angle QNR = 180^\circ$। আবার চতুর্ভুজ $AQNR$-এ অভিলম্বদ্বয়ের কোণ $90^\circ$ হওয়ায় বিপরীত কোণদ্বয়ের সমষ্টি $A + \angle QNR = 180^\circ$। তুলনা করে পাই: $r_1 + r_2 = A$। অতএব মোট বিচ্যুতি কোণ $\delta = i_1 + i_2 - A$।</t>
@@ -2269,11 +2164,6 @@
           <t>সরু প্রিজমের (Thin Prism, যেখানে প্রতিসারক কোণ $A &lt; 10^\circ$) ক্ষেত্রে প্রমাণ করো যে বিচ্যুতি কোণ আপতন কোণের ওপর প্রায় নির্ভর করে না এবং তা $\delta = (\mu - 1) A$।</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>সরু প্রিজমে কোণ $A$ অতি ক্ষুদ্র হওয়ায় সমস্ত কোণ ($i_1, r_1, r_2, i_2$) ক্ষুদ্র হয়। ফলে ক্ষুদ্র কোণের জন্য $\sin \theta \approx \theta$ লেখা যায়। প্রথম তলে স্নেলের সূত্র: $\mu = \frac{\sin i_1}{\sin r_1} \approx \frac{i_1}{r_1} \implies i_1 \approx \mu r_1$। দ্বিতীয় তলে স্নেলের সূত্র: $\mu = \frac{\sin i_2}{\sin r_2} \approx \frac{i_2}{r_2} \implies i_2 \approx \mu r_2$। মোট বিচ্যুতি কোণ $\delta = i_1 + i_2 - A = \mu r_1 + \mu r_2 - A = \mu(r_1 + r_2) - A$। আমরা জানি $r_1 + r_2 = A$। মান বসালে পাই: $\delta = \mu A - A = (\mu - 1)A$। এই সমীকরণ দেখায় যে সরু প্রিজমের বিচ্যুতি কোণ আপতন কোণের ওপর প্রায় সম্পূর্ণ স্বাধীন এবং তা কেবল উপাদানের প্রতিসরাঙ্ক ও প্রিজম কোণের গুণফল।</t>
@@ -2319,11 +2209,6 @@
           <t>স্বচ্ছ মাধ্যমে আলোর তরঙ্গদৈর্ঘ্যের সাথে প্রতিসরাঙ্কের পরিবর্তনের পরীক্ষালব্ধ কশির সমীকরণটি (Cauchy's Dispersion Formula) লেখো। দৃশ্যমান বর্ণালির লাল ও বেগুনি আলোর মধ্যে প্রিজমে কোন বর্ণের বিচ্যুতি বেশি হয় এবং কেন?</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>১৮৩৬ সালে অগাস্টিন-লুই কশি প্রতিপাদন করেন যে মাধ্যমে আলোর প্রতিসরাঙ্ক তরঙ্গদৈর্ঘ্যের ওপর নির্ভরশীল: $\mu(\lambda) = A + \frac{B}{\lambda^2} + \frac{C}{\lambda^4} + \dots$, যেখানে $A, B, C$ হলো মাধ্যমের ইতিবাচক ধ্রুবক। দৃশ্যমান বর্ণালিতে লাল আলোর তরঙ্গদৈর্ঘ্য সর্বাধিক ($\lambda_{\text{red}} \approx 700\text{ nm}$) এবং বেগুনি আলোর তরঙ্গদৈর্ঘ্য সর্বনিম্ন ($\lambda_{\text{violet}} \approx 400\text{ nm}$)। কশির সূত্রানুযায়ী $\lambda_{\text{violet}} &lt; \lambda_{\text{red}} \implies \mu_{\text{violet}} &gt; \mu_{\text{red}}$। সরু প্রিজমের বিচ্যুতি সমীকরণ $\delta = (\mu - 1)A$ থেকে স্পষ্ট যে $\mu$ যার বেশি তার বিচ্যুতি বেশি। ফলে বেগুনি আলো সবচেয়ে বেশি বাঁকে এবং লাল আলো সবচেয়ে কম বাঁকে।</t>
@@ -2369,11 +2254,6 @@
           <t>প্রিজমের উপাদানের কৌণিক বিচ্ছুরণ (Angular Dispersion, $\theta$) এবং বিচ্ছুরণ ক্ষমতা (Dispersive Power, $\omega$)-এর সংজ্ঞা দাও। লাল, হলুদ ও বেগুনি বর্ণের প্রতিসরাঙ্কের মাধ্যমে $\omega$-এর সমীকরণ প্রতিষ্ঠা করো।</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>১) কৌণিক বিচ্ছুরণ ($\theta$): প্রিজম থেকে নির্গত চরম দুটি বর্ণ (বেগুনি ও লাল)-এর বিচ্যুতির পার্থক্যকে কৌণিক বিচ্ছুরণ বলে: $\theta = \delta_v - \delta_r$। সরু প্রিজমে $\delta_v = (\mu_v - 1)A$ এবং $\delta_r = (\mu_r - 1)A$ বসালে পাই: $\theta = (\mu_v - \mu_r)A$। ২) বিচ্ছুরণ ক্ষমতা ($\omega$): কৌণিক বিচ্ছুরণ এবং মধ্যবর্তী হলুদ বর্ণের গড় বিচ্যুতির ($\delta_y$) অনুপাতকে ঐ উপাদানের বিচ্ছুরণ ক্ষমতা বলে: $\omega \equiv \frac{\delta_v - \delta_r}{\delta_y}$। মান বসালে: $\omega = \frac{(\mu_v - \mu_r)A}{(\mu_y - 1)A} = \frac{\mu_v - \mu_r}{\mu_y - 1}$। লক্ষণীয় যে বিচ্ছুরণ ক্ষমতা প্রিজমের কোণ $A$-এর ওপর নির্ভর করে না, এটি বিশুদ্ধভাবে উপাদানের একটি অন্তর্নিহিত ধর্ম।</t>
@@ -2419,11 +2299,6 @@
           <t>ক্রাউন কাঁচ ($A_1, \mu_1$) এবং ফ্লিন্ট কাঁচের ($A_2, \mu_2$) দুটি সরু প্রিজমকে বিপরীতমুখে যুক্ত করে এমন একটি সমবায় তৈরি করা হলো যা কোনো নিট গড় বিচ্যুতি ঘটায় না। দ্বিতীয় প্রিজমের কোণ $A_2$-এর শর্ত এবং লব্ধি কৌণিক বিচ্ছুরণের রাশিমালা নির্ণয় করো। ডিরেক্ট ভিশন স্পেকট্রোস্কোপে এর ভূমিকা কী?</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>নিট গড় বিচ্যুতি শূন্য হওয়ার শর্ত: $\delta_{\text{net}} = \delta_1 + \delta_2 = 0 \implies (\mu_1 - 1)A_1 + (\mu_2 - 1)A_2 = 0 \implies A_2 = -\left(\frac{\mu_1 - 1}{\mu_2 - 1}\right) A_1$ (ঋণাত্মক চিহ্ন নির্দেশ করে দ্বিতীয় প্রিজমটি উল্টো বসাতে হবে)। লব্ধি কৌণিক বিচ্ছুরণ $\theta_{\text{net}} = \theta_1 + \theta_2 = (\mu_{v1} - \mu_{r1})A_1 + (\mu_{v2} - \mu_{r2})A_2 = (\mu_1 - 1)A_1 \omega_1 + (\mu_2 - 1)A_2 \omega_2$। $A_2$-এর মান বসালে পাই: $\theta_{\text{net}} = (\mu_1 - 1)A_1 (\omega_1 - \omega_2) = \delta_1 (\omega_1 - \omega_2) \neq 0$ (যেহেতু ক্রাউন ও ফ্লিন্ট কাঁচের বিচ্ছুরণ ক্ষমতা $\omega_1 \neq \omega_2$)। ফলে আলো সোজাসুজি নির্গত হয়েও সুন্দরভাবে বিভিন্ন রঙে বিশ্লিষ্ট হয়।</t>
@@ -2469,11 +2344,6 @@
           <t>দুটি ভিন্ন উপাদানের প্রিজমকে বিপরীতমুখে সংযুক্ত করে একটি অবর্ণক প্রিজম সমবায় (Achromatic Prism) তৈরি করার শর্ত প্রতিপাদন করো যাতে কোনো বর্ণ বিচ্ছুরণ না ঘটে কিন্তু একটি নিট বিচ্যুতি বজায় থাকে।</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>নিট কৌণিক বিচ্ছুরণ শূন্য হওয়ার শর্ত: $\theta_{\text{net}} = \theta_1 + \theta_2 = 0 \implies (\mu_{v1} - \mu_{r1})A_1 + (\mu_{v2} - \mu_{r2})A_2 = 0 \implies \frac{A_1}{A_2} = -\frac{\mu_{v2} - \mu_{r2}}{\mu_{v1} - \mu_{r1}}$। বিচ্ছুরণ ক্ষমতার মাধ্যমে লিখলে: $(\mu_1 - 1)\omega_1 A_1 + (\mu_2 - 1)\omega_2 A_2 = 0 \implies \delta_1 \omega_1 + \delta_2 \omega_2 = 0$। মোট বিচ্যুতি $\delta_{\text{net}} = \delta_1 + \delta_2 = \delta_1 - \delta_1 \frac{\omega_1}{\omega_2} = \delta_1 \left(1 - \frac{\omega_1}{\omega_2}\right)$। যেহেতু $\omega_1 \neq \omega_2$, তাই নিট বিচ্যুতি অশূন্য থাকে। এর ফলে সাদা আলো রঙে না ভেঙে অবিকৃত সাদা আলো হিসেবেই একটি নির্দিষ্ট কোণে বিচ্যুত হয়ে নির্গত হয়।</t>
@@ -2519,11 +2389,6 @@
           <t>একটি প্রিজমের প্রতিসারক কোণ $A$ এবং উপাদানের প্রতিসরাঙ্ক $\mu$ হলে আপতন কোণ $i_1$-এর মান যাই হোক না কেন, দ্বিতীয় তল থেকে আলো কখনই নির্গত হতে পারবে না (পূর্ণ অভ্যন্তরীণ প্রতিফলনে আটকে যাবে) যদি $A &gt; 2\theta_c$ হয়। এটি গাণিতিকভাবে প্রমাণ করো।</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>দ্বিতীয় তল থেকে আলো নির্গত না হওয়ার শর্ত হলো সমস্ত আপতন কোণের জন্য $r_2 &gt; \theta_c$ হওয়া। আমরা জানি $r_1 + r_2 = A \implies r_2 = A - r_1$। $r_2$ সর্বনিম্ন হবে যখন $r_1$ সর্বোচ্চ হবে। স্নেলের সূত্রে $r_1$ সর্বোচ্চ হয় যখন প্রথম তলে আপতন কোণ সর্বোচ্চ হয়, অর্থাৎ গ্র্যাজিং আপতনে $i_1 \to 90^\circ$ হলে $r_{1,\max} = \theta_c$। অতএব $r_2$-এর সর্বনিম্ন সম্ভাব্য মান হলো $r_{2,\min} = A - r_{1,\max} = A - \theta_c$। এই সর্বনিম্ন মানটিও যদি সংকট কোণের চেয়ে বড় হয়, তবে কোনো রশ্মিই দ্বিতীয় তল ভেদ করে বের হতে পারবে না: $r_{2,\min} &gt; \theta_c \implies A - \theta_c &gt; \theta_c \implies A &gt; 2\theta_c$। যেমন কাঁচের $\theta_c \approx 42^\circ$ হলে প্রিজম কোণ $A &gt; 84^\circ$ হলে কোনো আলো নির্গত হয় না।</t>
@@ -2569,11 +2434,6 @@
           <t>একটি ফাঁপা কাঁচের প্রিজমের অভ্যন্তরে একটি অজানা তরল পূর্ণ করে ন্যূনতম বিচ্যুতি কোণ মেপে তরলটির প্রতিসরাঙ্ক নির্ণয় করা হয়। ফাঁপা পাত্রের পাতলা কাঁচের দেয়াল দুটি তরলের প্রতিসরাঙ্ক নির্ণয়ের সমীকরণকে প্রভাবিত করে না কেন?</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>ফাঁপা প্রিজমের দেয়াল তৈরি হয় সুষম পাতলা সমান্তরাল কাঁচের প্লেট দিয়ে। বাতাস থেকে কাঁচে এবং কাঁচ থেকে তরলে আলো প্রতিসরিত হওয়ার সময় কাঁচের উভয় পৃষ্ঠের আপতন ও নির্গমন কোণ স্নেলের সূত্রানুযায়ী এমন হয় যে: $1 \cdot \sin i = \mu_{\text{glass}} \sin r_{\text{glass}} = \mu_{\text{liquid}} \sin r_{\text{liquid}}$। ফলে সমীকরণটিতে মধ্যবর্তী কাঁচের প্রতিসরাঙ্ক $\mu_{\text{glass}}$ সম্পূর্ণ কাটাকাটি হয়ে যায় এবং আলো সরাসরি বাতাস থেকে তরলে প্রবেশের সমতুল্য কৌণিক আচরণ করে। পাতলা কাঁচের ফলক কেবল সামান্য সমান্তরাল পার্শ্ব সরণ তৈরি করে কিন্তু কোনো অতিরিক্ত কোণ যোগ করে না। ফলে সাধারণ স্পেকট্রোমিটারে তরল প্রিজম দিয়ে যেকোনো উদ্বায়ী বা রাসায়নিক তরলের প্রতিসরাঙ্ক অতি নিখুঁতভাবে মাপা যায়।</t>
@@ -2619,11 +2479,6 @@
           <t>একটি গোলাকার বৃষ্টির ফোঁটায় (প্রতিসরাঙ্ক $\mu$) সূর্যালোক প্রবেশ করে একবার পূর্ণ অভ্যন্তরীণ প্রতিফলিত হয়ে নির্গত হলে মোট বিচ্যুতি কোণের সমীকরণ প্রতিষ্ঠা করো। বিচ্যুতি কোণ সর্বনিম্ন হওয়ার শর্ত প্রয়োগ করে প্রমাণ করো যে প্রাথমিক রামধনুর কোণ প্রায় $৪২^\circ$ হয়।</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>আলোর ফোঁটায় প্রবেশকালে বিচ্যুতি $(i - r)$, অভ্যন্তরীণ প্রতিফলনে বিচ্যুতি $(180^\circ - 2r)$ এবং নির্গমনকালে বিচ্যুতি $(i - r)$। মোট বিচ্যুতি: $\delta = (i - r) + (180^\circ - 2r) + (i - r) = 180^\circ + 2i - 4r$। বিচ্যুতি চরম (ন্যূনতম) হওয়ার শর্ত: $\frac{d\delta}{di} = 0 \implies 2 - 4\frac{dr}{di} = 0 \implies \frac{dr}{di} = \frac{1}{2}$। স্নেলের সূত্র $\sin i = \mu \sin r$-কে ব্যবকলন করে: $\cos i di = \mu \cos r dr \implies \frac{dr}{di} = \frac{\cos i}{\mu \cos r} = \frac{1}{2} \implies 2\cos i = \mu \cos r$। উভয়পাশে বর্গ করে: $4\cos^2 i = \mu^2(1 - \sin^2 r) = \mu^2 - \sin^2 i = \mu^2 - (1 - \cos^2 i) \implies 3\cos^2 i = \mu^2 - 1 \implies \cos i = \sqrt{\frac{\mu^2 - 1}{3}}$। পানির জন্য $\mu = 4/3$ বসালে: $\cos i = \sqrt{\frac{16/9 - 1}{3}} = \sqrt{7/27} \approx 0.509 \implies i \approx 59.4^\circ$ এবং $r \approx 40.2^\circ$। মোট বিচ্যুতি $\delta \approx 180^\circ + 2(59.4^\circ) - 4(40.2^\circ) \approx 138^\circ$। এর সম্পূরক কোণ $180^\circ - 138^\circ = 42^\circ$। এই কোণে আলোকরশ্মির ঘনত্ব সর্বোচ্চ হওয়ায় আকাশে চমৎকার প্রাথমিক রামধনু দৃশ্যমান হয়।</t>
@@ -2669,11 +2524,6 @@
           <t>$\mu_1$ প্রতিসরাঙ্কের মাধ্যম থেকে $\mu_2$ প্রতিসরাঙ্কের মাধ্যমে আলো প্রবেশকালে $R$ বক্রতার ব্যাসার্ধের একটি গোলীয় তলে প্রতিসরণের সাধারণ সমীকরণ $\frac{\mu_2}{v} - \frac{\mu_1}{u} = \frac{\mu_2 - \mu_1}{R}$ জ্যামিতিক চিত্রের সাহায্যে প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>প্রধান অক্ষের ওপর $O$ বিন্দুতে বস্তু অবস্থিত এবং $I$ বিন্দুতে প্রতিবিম্ব গঠিত হয়। আপতন বিন্দু $M$ থেকে অক্ষে লম্ব $MP$ টানি। কোণগুলো ক্ষুদ্র হওয়ায় $\alpha \approx \frac{MP}{-u}$, $\beta \approx \frac{MP}{R}$, $\gamma \approx \frac{MP}{v}$। ত্রিভুজ $OMC$ থেকে আপতন কোণ $i = \alpha + \beta$। ত্রিভুজ $MIC$ থেকে প্রতিসরণ কোণ $r = \beta - \gamma$। স্নেলের সূত্রানুযায়ী উপাক্ষীয় রশ্মির জন্য: $\mu_1 i \approx \mu_2 r \implies \mu_1(\alpha + \beta) = \mu_2(\beta - \gamma) \implies \mu_1 \alpha + \mu_2 \gamma = (\mu_2 - \mu_1)\beta$। মান বসালে: $\mu_1 \left(\frac{MP}{-u}\right) + \mu_2 \left(\frac{MP}{v}\right) = (\mu_2 - \mu_1)\left(\frac{MP}{R}\right)$। উভয়পাশ থেকে $MP$ কাটাকাটি করলে পাই: $\frac{\mu_2}{v} - \frac{\mu_1}{u} = \frac{\mu_2 - \mu_1}{R}$।</t>
@@ -2719,11 +2569,6 @@
           <t>দুটি গোলীয় প্রতিসারক তলের ধারাবাহিক প্রতিসরণ বিবেচনা করে একটি পাতলা লেন্সের ফোকাস দূরত্বের লেন্স প্রস্তুতকারকের সূত্র $\frac{1}{f} = (\mu - 1)\left(\frac{1}{R_1} - \frac{1}{R_2}\right)$ প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>লেন্সের বেধ $t \to 0$ বিবেচনা করি। প্রথম তলে ($R_1$) বাতাস থেকে কাঁচে প্রতিসরণ: $\frac{\mu}{v'} - \frac{1}{u} = \frac{\mu - 1}{R_1}$ ... (১)। এই মধ্যবর্তী প্রতিবিম্বটি দ্বিতীয় তলের জন্য অবাস্তব বস্তু হিসেবে কাজ করে। দ্বিতীয় তলে ($R_2$) কাঁচ থেকে বাতাসে প্রতিসরণ: $\frac{1}{v} - \frac{\mu}{v'} = \frac{1 - \mu}{R_2} = -\frac{\mu - 1}{R_2}$ ... (২)। সমীকরণ (১) ও (২) সরাসরি যোগ করলে মধ্যবর্তী পদ $\frac{\mu}{v'}$ সম্পূর্ণ বাতিল হয়ে যায়: $\frac{1}{v} - \frac{1}{u} = (\mu - 1)\left(\frac{1}{R_1} - \frac{1}{R_2}\right)$। অসীমে থাকা বস্তুর জন্য ($u = \infty$) প্রতিবিম্ব ফোকাসে গঠিত হয় ($v = f$), ফলে $\frac{1}{f} = (\mu - 1)\left(\frac{1}{R_1} - \frac{1}{R_2}\right)$।</t>
@@ -2769,11 +2614,6 @@
           <t>বাতাসে একটি কাঁচের ($\mu_g = 1.5$) উত্তল লেন্সের ফোকাস দূরত্ব $f_a$। লেন্সটিকে পানিতে ($\mu_w = 4/3$) নিমজ্জিত করলে এর নতুন ফোকাস দূরত্ব $f_w$ পূর্বের কত গুণ হবে? যদি লেন্সটিকে কাঁচের চেয়ে ঘন কোনো তরলে ($\mu_l = 1.6$) নিমজ্জিত করা হয় তবে লেন্সের প্রকৃতি কেমন হবে?</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>বাতাসে লেন্সের সূত্র: $\frac{1}{f_a} = (\mu_g - 1)\left(\frac{1}{R_1} - \frac{1}{R_2}\right) = (1.5 - 1) K = 0.5 K$। পানিতে লেন্সের কার্যকর প্রতিসরাঙ্ক $\mu = \frac{\mu_g}{\mu_w} = \frac{1.5}{4/3} = \frac{9}{8} = 1.125$। পানিতে ফোকাস দূরত্ব: $\frac{1}{f_w} = \left(\frac{9}{8} - 1\right) K = \frac{1}{8} K = 0.125 K$। অনুপাত নিলে: $\frac{f_w}{f_a} = \frac{0.5 K}{0.125 K} = 4 \implies f_w = 4 f_a$। অর্থাৎ পানিতে নিমজ্জিত করলে ফোকাস দূরত্ব চারগুণ বৃদ্ধি পায়। যদি তরলের প্রতিসরাঙ্ক কাঁচের চেয়ে বেশি হয় ($\mu_l &gt; \mu_g$), তবে $\left(\frac{\mu_g}{\mu_l} - 1\right) &lt; 0$ ঋণাত্মক হয়ে যায়। ফলে উত্তল লেন্সের ফোকাস দূরত্ব ঋণাত্মক হয়ে এটি একটি অপসারী লেন্সের ন্যায় কাজ করে।</t>
@@ -2870,11 +2710,6 @@
           <t>একটি সমতল-উত্তল লেন্সের ($\mu = 1.5, R = 20\text{ cm}$) সমতল পৃষ্ঠে রূপার প্রলেপ (Silvering) দিয়ে একটি প্রতিফলক তৈরি করা হলো। ব্যবস্থাটি কোন ধরনের দর্পণ হিসেবে কাজ করবে এবং এর তুল্য ফোকাস দূরত্ব কত হবে? ক্ষমতা সমীকরণ $P = 2P_L + P_M$ প্রয়োগ করো।</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>সিলভারিং করা লেন্সে আলো প্রথমে লেন্সে প্রতিসরিত হয়, তারপর দর্পণে প্রতিফলিত হয় এবং পুনরায় লেন্স দিয়ে প্রতিসরিত হয়ে বেরিয়ে আসে। ফলে ব্যবস্থার মোট ক্ষমতা হলো লেন্সের ক্ষমতার দ্বিগুণ এবং দর্পণের ক্ষমতার যোগফল: $P = 2 P_L + P_M$। সমতল-উত্তল লেন্সের ক্ষমতা $P_L = \frac{1}{f_L} = (\mu - 1)\frac{1}{R} = \frac{0.5}{0.2} = +2.5\text{ D}$। সমতল পৃষ্ঠের দর্পণের বক্রতার ব্যাসার্ধ অসীম হওয়ায় দর্পণের ক্ষমতা $P_M = -\frac{1}{f_M} = 0$। মোট ক্ষমতা $P = 2(2.5) + 0 = +5.0\text{ D}$। দর্পণের ক্ষেত্রে ক্ষমতা ও ফোকাস দূরত্বের সম্পর্ক $P = -\frac{1}{F} \implies F = -\frac{1}{P} = -\frac{1}{5} = -0.2\text{ m} = -20\text{ cm}$। ফোকাস দূরত্ব ঋণাত্মক হওয়ায় ব্যবস্থাটি একটি ২০ সেমি ফোকাস দূরত্বের অবতল দর্পণ হিসেবে কাজ করে।</t>
@@ -2920,11 +2755,6 @@
           <t>পূর্ববর্তী লেন্সটির ($\mu = 1.5, R = 20\text{ cm}$) সমতল পৃষ্ঠের বদলে যদি বক্র পৃষ্ঠটিতে রূপার প্রলেপ দেওয়া হয়, তবে ব্যবস্থাটির তুল্য ফোকাস দূরত্ব কত হবে?</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>বক্র পৃষ্ঠে সিলভারিং করলে প্রতিফলকটি একটি অবতল দর্পণে পরিণত হয় যার বক্রতার ব্যাসার্ধ $R = 20\text{ cm}$। দর্পণটির ফোকাস দূরত্ব $f_M = -R/2 = -10\text{ cm} = -0.1\text{ m}$। দর্পণের ক্ষমতা $P_M = -\frac{1}{f_M} = -\frac{1}{-0.1} = +10\text{ D}$। লেন্সের ক্ষমতা পূর্বের ন্যায় $P_L = +2.5\text{ D}$। মোট তুল্য ক্ষমতা: $P = 2 P_L + P_M = 2(2.5) + 10 = 5 + 10 = +15\text{ D}$। তুল্য ফোকাস দূরত্ব $F = -\frac{1}{P} = -\frac{1}{15}\text{ m} = -\frac{100}{15}\text{ cm} = -\frac{20}{3}\text{ cm} \approx -6.67\text{ cm}$।</t>
@@ -2970,11 +2800,6 @@
           <t>$R$ ব্যাসার্ধ এবং $\mu$ প্রতিসরাঙ্কের একটি নিরেট কাঁচের গোলকের ওপর অক্ষের সমান্তরাল আলোকরশ্মি আপতিত হলো। গোলকের কেন্দ্র থেকে কত দূরত্বে এই রশ্মিগুলো ফোকাসিত হবে? $\mu = 1.5$ হলে গোলকের পৃষ্ঠ থেকে ফোকাসের দূরত্ব কত?</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>প্রথম তলে প্রতিসরণ ($R_1 = +R$): বাতাস থেকে কাঁচে অসীম থেকে রশ্মি আসায় ($u = -\infty$): $\frac{\mu}{v_1} - \frac{1}{-\infty} = \frac{\mu - 1}{R} \implies v_1 = \frac{\mu R}{\mu - 1}$। এই প্রতিবিম্বটি দ্বিতীয় তলের জন্য বস্তু হিসেবে কাজ করে। প্রথম পৃষ্ঠ থেকে দ্বিতীয় পৃষ্ঠের দূরত্ব হলো ব্যাস $2R$। দ্বিতীয় তলের জন্য বস্তুর দূরত্ব $u_2 = v_1 - 2R = \frac{\mu R}{\mu - 1} - 2R = \frac{(2 - \mu)R}{\mu - 1}$। দ্বিতীয় তলে কাঁচ থেকে বাতাসে প্রতিসরণ ($R_2 = -R$): $\frac{1}{v_2} - \frac{\mu}{u_2} = \frac{1 - \mu}{-R} = \frac{\mu - 1}{R}$। মান বসিয়ে সমাধান করলে দ্বিতীয় পৃষ্ঠ থেকে প্রতিবিম্বের দূরত্ব পাওয়া যায়: $v_2 = \frac{(2 - \mu)R}{2(\mu - 1)}$। $\mu = 1.5$ বসালে: $v_2 = \frac{(2 - 1.5)R}{2(1.5 - 1)} = \frac{0.5 R}{2(0.5)} = \frac{R}{2}$। কেন্দ্র থেকে মোট দূরত্ব $R + R/2 = 1.5 R$।</t>
@@ -3020,11 +2845,6 @@
           <t>$f = 15\text{ cm}$ ফোকাস দূরত্বের একটি উত্তল লেন্সের পেছনে একটি সমতল দর্পণ রাখা হলো। লেন্সের সামনে প্রধান অক্ষে কত দূরত্বে একটি বিন্দু আলোক উৎস রাখলে দর্পণ থেকে প্রতিফলিত হয়ে আলো পুনরায় উৎসের অবস্থানেই ফিরে আসবে?</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>আলোর বিপরীতমুখিতা নীতি অনুসারে, প্রতিফলিত রশ্মি যদি হুবহু একই পথে ফিরে এসে উৎসে মিলিত হতে চায়, তবে দর্পণের পৃষ্ঠে রশ্মিগুলোকে অবশ্যই লম্বভাবে আপতিত হতে হবে ($i = 0$)। সমতল দর্পণে লম্বভাবে আপতিত হওয়ার অর্থ হলো লেন্স থেকে নির্গত রশ্মিগুলো অবশ্যই প্রধান অক্ষের সমান্তরাল হতে হবে। একটি উত্তল লেন্সে প্রধান অক্ষের সমান্তরাল রশ্মিগুচ্ছ তখনই তৈরি হয় যখন বিন্দু আলোক উৎসটি লেন্সের প্রথম প্রধান ফোকাসে অবস্থান করে। অতএব উৎসটিকে লেন্স থেকে ঠিক তার ফোকাস দূরত্বের সমান দূরত্বে ($u = f = 15\text{ cm}$) স্থাপন করতে হবে। লক্ষণীয় যে লেন্স ও সমতল দর্পণের মধ্যকার ব্যবধান যাই হোক না কেন, এই ফলাফল সত্য থাকে।</t>
@@ -3070,11 +2890,6 @@
           <t>একটি ফোকাস দূরত্ব $f$ বিশিষ্ট পাতলা উত্তল লেন্সের সামনে $u = 2f$ দূরত্বে একটি বস্তু রাখা আছে। লেন্সটিকে তার প্রধান অক্ষের লম্ব দিকে খাড়া $\Delta y$ পরিমাণ উপরে সরিয়ে নিলে প্রতিবিম্বের অবস্থানের উল্লম্ব স্থানচ্যুতি কত হবে?</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>বস্তু যখন $u = 2f$ দূরত্বে থাকে, তখন প্রতিবিম্ব $v = 2f$ দূরত্বে গঠিত হয় এবং রৈখিক বিবর্ধন $m = -\frac{v}{u} = -1$। লেন্সটিকে উল্লম্বভাবে $\Delta y$ উপরে সরালে লেন্সের অপটিক্যাল অক্ষও $\Delta y$ উপরে উঠে যায়। ফলে মূল বস্তুটি নতুন অপটিক্যাল অক্ষের সাপেক্ষে $-\Delta y$ নিচে নেমে গেছে বলে মনে হয় ($y_{\text{obj}}' = -\Delta y$)। লেন্সের সাপেক্ষে প্রতিবিম্বের নতুন উচ্চতা $y_{\text{img}}' = m y_{\text{obj}}' = (-1)(-\Delta y) = +\Delta y$ (অর্থাৎ নতুন অক্ষের ওপরে)। কিন্তু নতুন অক্ষটি তো পূর্বের অক্ষের চেয়ে $\Delta y$ উপরে অবস্থিত! অতএব মূল স্থির রেফারেন্স অক্ষের সাপেক্ষে প্রতিবিম্বের চূড়ান্ত অবস্থান: $y_{\text{final}} = \text{অক্ষের স্থানচ্যুতি} + y_{\text{img}}' \dots$ সতর্ক হিসাব: বস্তু অক্ষের নিচে $\Delta y$, ফলে প্রতিবিম্ব অক্ষের উপরে $\Delta y$। যেহেতু লেন্স নিজেই $\Delta y$ উঠেছে, তাই মূল তল সাপেক্ষে স্থানচ্যুতি $2\Delta y$ হয়।</t>
@@ -3120,11 +2935,6 @@
           <t>একটি প্রতিসম উভোত্তল কাঁচের লেন্সের অর্ধেকাংশ পানিতে ($\mu_w = 4/3$) এবং বাকি অর্ধেকাংশ বাতাসে রাখা হলো। প্রধান অক্ষের ওপর অবস্থিত একটি বিন্দু বস্তুর জন্য এই ব্যবস্থাটি কয়টি প্রতিবিম্ব তৈরি করবে এবং তাদের তীব্রতার তুলনা কী হবে?</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>যেহেতু লেন্সের উপরের অর্ধেকাংশ বাতাসে এবং নিচের অর্ধেকাংশ পানিতে নিমজ্জিত, তাই লেন্সের দুটি অর্ধাংশ দুটি ভিন্ন ফোকাস দূরত্বের লেন্সের ন্যায় স্বাধীনভাবে কাজ করে। উপরের অর্ধাংশের ফোকাস দূরত্ব $f_a$ এবং নিচের অর্ধাংশের ফোকাস দূরত্ব $f_w \approx 4 f_a$। ফলে প্রধান অক্ষের ওপর অবস্থিত একটিমাত্র বস্তু থেকে নির্গত আলোকরশ্মির উপরের অর্ধেক $f_a$ অনুযায়ী প্রতিসরিত হয়ে কাছে একটি প্রতিবিম্ব তৈরি করবে এবং নিচের অর্ধেক রশ্মি $4 f_a$ অনুযায়ী প্রতিসরিত হয়ে দূরে দ্বিতীয় আরেকটি প্রতিবিম্ব তৈরি করবে। যেহেতু আপতিত আলোর ক্ষেত্রফল সমান দুই ভাগে বিভক্ত হয়েছে, তাই প্রতিটি প্রতিবিম্বের উজ্জ্বলতা বা তীব্রতা মূল একক প্রতিবিম্বের ঠিক অর্ধেক ($৫০\%$) হবে।</t>
@@ -3170,11 +2980,6 @@
           <t>$f_1$ ও $f_2$ ফোকাস দূরত্বের দুটি পাতলা লেন্স পরস্পরের সংস্পর্শে স্থাপন করা হলে তাদের তুল্য ফোকাস দূরত্বের সমীকরণ $\frac{1}{F} = \frac{1}{f_1} + \frac{1}{f_2}$ এবং তুল্য ক্ষমতা $P = P_1 + P_2$ প্রতিপাদন করো। লেন্স দুটির ক্ষমতা সমান ও বিপরীত হলে তুল্য ক্ষমতা কত?</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>প্রথম লেন্সের সমীকরণ: $\frac{1}{v'} - \frac{1}{u} = \frac{1}{f_1}$। এই প্রতিবিম্বটি দ্বিতীয় লেন্সের জন্য বস্তু হিসেবে কাজ করে। দ্বিতীয় লেন্সের সমীকরণ: $\frac{1}{v} - \frac{1}{v'} = \frac{1}{f_2}$। সমীকরণ দুটি যোগ করলে মধ্যবর্তী পদ $\frac{1}{v'}$ বাতিল হয়ে যায়: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f_1} + \frac{1}{f_2}$। তুল্য লেন্সের সমীকরণ $\frac{1}{v} - \frac{1}{u} = \frac{1}{F}$-এর সাথে তুলনা করলে পাই: $\frac{1}{F} = \frac{1}{f_1} + \frac{1}{f_2}$। ক্ষমতার সংজ্ঞামতে $P \equiv \frac{1}{f}$, অতএব $P = P_1 + P_2$। যদি একটি $+2\text{ D}$ উত্তল এবং অপরটি $-2\text{ D}$ অবতল লেন্স সংস্পর্শে রাখা হয়, তবে লব্ধি ক্ষমতা $P = +2 - 2 = 0$ এবং ফোকাস দূরত্ব $F = \frac{1}{0} \to \infty$ হয়।</t>
@@ -3220,11 +3025,6 @@
           <t>$f_1$ ও $f_2$ ফোকাস দূরত্বের দুটি পাতলা লেন্স পরস্পরের সমান্তরালে $d$ দূরত্বে অবস্থিত। ম্যাট্রিক্স মেথড বা রশ্মি অনুসরণ করে প্রমাণ করো যে সমবায়ের তুল্য ক্ষমতা $P = P_1 + P_2 - d P_1 P_2$ এবং তুল্য ফোকাস দূরত্ব $\frac{1}{F} = \frac{1}{f_1} + \frac{1}{f_2} - \frac{d}{f_1 f_2}$।</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>প্রধান অক্ষের সমান্তরাল উচ্চতা $h_1$-এ প্রথম লেন্সে আপতিত রশ্মির বিচ্যুতি কোণ $\delta_1 = h_1 P_1 = \frac{h_1}{f_1}$। $d$ দূরত্ব অতিক্রম করে দ্বিতীয় লেন্সে পৌঁছানোর সময় রশ্মির উচ্চতা কমে হয় $h_2 = h_1 - d \delta_1 = h_1 - d h_1 P_1 = h_1(1 - d P_1)$। দ্বিতীয় লেন্সে অতিরিক্ত বিচ্যুতি ঘটে $\delta_2 = h_2 P_2 = h_1(1 - d P_1)P_2$। সমগ্র সমবায়ের মোট লব্ধি বিচ্যুতি কোণ: $\delta = \delta_1 + \delta_2 = h_1 P_1 + h_1 P_2 - d h_1 P_1 P_2 = h_1 [P_1 + P_2 - d P_1 P_2]$। কিন্তু তুল্য লেন্সের সংজ্ঞামতে $\delta = h_1 P$। অতএব তুল্য ক্ষমতা $P = P_1 + P_2 - d P_1 P_2$। ফোকাস দূরত্বের এককে লিখলে: $\frac{1}{F} = \frac{1}{f_1} + \frac{1}{f_2} - \frac{d}{f_1 f_2}$।</t>
@@ -3270,11 +3070,6 @@
           <t>$f$ ফোকাস দূরত্বের একটি উভোত্তল লেন্সকে তার প্রধান অক্ষের লম্ব তলে কেটে দুটি সমান সমতল-উত্তল লেন্সে বিভক্ত করা হলো। প্রতিটি নতুন খণ্ডের ফোকাস দূরত্ব কত হবে? খণ্ড দুটিকে (ক) সমতল পৃষ্ঠ মুখোমুখি রেখে এবং (খ) বক্র পৃষ্ঠ মুখোমুখি রেখে জোড়া লাগালে তুল্য ফোকাস দূরত্ব কত হবে?</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>মূল উভোত্তল লেন্সের জন্য $\frac{1}{f} = (\mu - 1)\left(\frac{1}{R} - \frac{1}{-R}\right) = \frac{2(\mu - 1)}{R}$। লম্বভাবে কাটলে প্রতিটি খণ্ড একটি সমতল-উত্তল লেন্সে পরিণত হয় যার $R_1 = R$ এবং $R_2 = \infty$। ফলে নতুন ফোকাস দূরত্ব $\frac{1}{f'} = (\mu - 1)\left(\frac{1}{R} - 0\right) = \frac{\mu - 1}{R} = \frac{1}{2f} \implies f' = 2f$। অর্থাৎ প্রতিটি অংশের ক্ষমতা অর্ধেক এবং ফোকাস দূরত্ব দ্বিগুণ হয়। ক ও খ) খণ্ড দুটিকে যেভাবেই পরস্পরের সংস্পর্শে রাখা হোক না কেন, তাদের ক্ষমতার যোগফল হবে: $P_{\text{eq}} = P' + P' = \frac{1}{2f} + \frac{1}{2f} = \frac{1}{f}$। ফলে তুল্য ফোকাস দূরত্ব পুনরায় পূর্বের $F = f$-এ ফিরে আসে।</t>
@@ -3371,11 +3166,6 @@
           <t>একটি উত্তল লেন্সকে অনুভূমিকভাবে কেটে দুটি খণ্ডকে পরস্পর থেকে $d$ দূরত্বে ফাঁক করে রাখা হলো (Billet's Split Lens)। লেন্সের অক্ষের ওপর স্থাপিত একটি বিন্দু উৎস থেকে দুটি সুসংগত উৎস (coherent sources) কীভাবে তৈরি হয় এবং ব্যতিচার ঝালর সৃষ্টিতে এর ভূমিকা কী?</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>বিলেটের বিভক্ত লেন্সে (Billet's Bilens) দুটি অর্ধ-লেন্সকে উল্লম্বভাবে $d$ ব্যবধানে রাখা হয়। লেন্স দুটির নিজস্ব প্রধান অক্ষ দুটিও $d$ দূরত্বে সমান্তরালভাবে অবস্থান করে। মূল অক্ষের ওপর অবস্থিত একক বিন্দু আলোক উৎসটি উপরের লেন্সের অক্ষের নিচে এবং নিচের লেন্সের অক্ষের উপরে থাকে। ফলে দুটি লেন্স যথাক্রমে দুটি বাস্তব প্রতিবিম্ব $S_1$ ও $S_2$ গঠন করে যাদের মধ্যবর্তী দূরত্ব $d' = d\left(1 + \frac{v}{u}\right)$। যেহেতু এই প্রতিবিম্ব দুটি একই মূল উৎস থেকে উৎপন্ন হয়েছে, তাই এরা নিখুঁত সুসংগত উৎস (coherent sources) হিসেবে আচরণ করে। এদের থেকে নির্গত আলো উপরিপাতিত হয়ে সামনের পর্দায় স্পষ্ট ব্যতিচার ঝালর (interference fringes) প্রদর্শন করে।</t>
@@ -3421,11 +3211,6 @@
           <t>উত্তল লেন্সের ফোকাস দূরত্ব নির্ণয়ের স্থানচ্যুতি পদ্ধতিতে পর্দা ও স্থির বস্তুর মধ্যবর্তী দূরত্ব $D$ ($D &gt; 4f$)। লেন্সের দুটি অবস্থানের জন্য পর্দায় স্পষ্ট প্রতিবিম্ব পাওয়া যায় যাদের ব্যবধান $d$। প্রমাণ করো যে লেন্সটির ফোকাস দূরত্ব $f = \frac{D^2 - d^2}{4D}$।</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>ধরি প্রথম অবস্থানে বস্তুর দূরত্ব $u_1$ এবং প্রতিবিম্ব দূরত্ব $v_1$। ফলে $u_1 + v_1 = D$। দ্বিতীয় অবস্থানে লেন্সের স্থানচ্যুতি $d$ হলে বিপরীতমুখিতা নীতি অনুসারে $u_2 = v_1$ এবং $v_2 = u_1$। ফলে $v_1 - u_1 = d$। সমীকরণ দুটি সমাধান করে পাই: $v_1 = \frac{D + d}{2}$ এবং $u_1 = \frac{D - d}{2}$। লেন্সের সমীকরণে মান বসালে: $\frac{1}{f} = \frac{1}{v_1} - \frac{1}{-u_1} = \frac{1}{v_1} + \frac{1}{u_1} = \frac{u_1 + v_1}{u_1 v_1} = \frac{D}{\left(\frac{D - d}{2}\right)\left(\frac{D + d}{2}\right)} = \frac{4D}{D^2 - d^2}$। উল্টে দিলে পাই: $f = \frac{D^2 - d^2}{4D}$। এই পদ্ধতিটি অত্যন্ত নির্ভরযোগ্য কারণ এতে লেন্সের সঠিক অপটিক্যাল কেন্দ্র না জেনেও কেবল লেন্সের স্থানচ্যুতি $d$ মেপে নির্ভুল ফোকাস দূরত্ব পাওয়া যায়।</t>
@@ -3471,11 +3256,6 @@
           <t>স্থানচ্যুতি পদ্ধতিতে লেন্সের দুটি অবস্থানে পর্দায় গঠিত প্রতিবিম্বদ্বয়ের আকার যথাক্রমে $I_1$ ও $I_2$ হলে প্রমাণ করো যে মূল বস্তুর প্রকৃত আকার $O = \sqrt{I_1 I_2}$। বিবর্ধনদ্বয়ের গুণফল $m_1 m_2 = 1$ কেন হয়?</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>প্রথম অবস্থানে বিবর্ধন $m_1 = \frac{I_1}{O} = \frac{v_1}{u_1}$। দ্বিতীয় অবস্থানে লেন্সের স্থান বিনিময়ের কারণে বস্তুর দূরত্ব ও প্রতিবিম্ব দূরত্ব পরস্পর বদলে যায় ($u_2 = v_1, v_2 = u_1$)। ফলে দ্বিতীয় অবস্থানে বিবর্ধন $m_2 = \frac{I_2}{O} = \frac{v_2}{u_2} = \frac{u_1}{v_1} = \frac{1}{m_1}$। অতএব বিবর্ধনদ্বয়ের গুণফল: $m_1 \times m_2 = \left(\frac{v_1}{u_1}\right)\left(\frac{u_1}{v_1}\right) = 1$। আকারের মাধ্যমে লিখলে: $\left(\frac{I_1}{O}\right)\left(\frac{I_2}{O}\right) = 1 \implies \frac{I_1 I_2}{O^2} = 1 \implies O^2 = I_1 I_2 \implies O = \sqrt{I_1 I_2}$। অর্থাৎ বস্তুর আকার প্রতিবিম্ব দুটির আকারের গুণোত্তর গড় (geometric mean)।</t>
@@ -3521,11 +3301,6 @@
           <t>একটি সমতল দর্পণের ওপর একটি উত্তল লেন্স রেখে তাদের মাঝে কয়েক ফোঁটা তরল দিলে একটি সমতল-অবতল তরল লেন্স গঠিত হয়। এই ব্যবস্থার সাহায্যে অজানা তরলের প্রতিসরাঙ্ক $\mu_l$ নির্ণয়ের কার্যপদ্ধতি ও সমীকরণটি লেখো।</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>দর্পণের ওপর লেন্স রাখলে আলো লেন্সে ঢুকে দর্পণে প্রতিফলিত হয়ে ফিরে আসে। শুষ্ক অবস্থায় পিন দিয়ে লম্বন দূর করে ফোকাস দূরত্ব $f_1$ মাপা হয় ($f_1 = R / [2(\mu_g - 1)] \implies R$ নির্ণীত হয়)। এরপর দর্পণ ও লেন্সের মাঝে তরল দিলে লেন্সের নিচের উত্তল পৃষ্ঠ এবং দর্পণের সমতল পৃষ্ঠের মধ্যবর্তী স্থানে একটি সমতল-অবতল (plano-concave) তরল লেন্স তৈরি হয় যার বক্রতার ব্যাসার্ধ লেন্সের নিচের পৃষ্ঠের সমান ($R$) এবং অপর পৃষ্ঠ সমতল ($\infty$)। তরল লেন্সের ক্ষমতা $P_l = (\mu_l - 1)\left(\frac{1}{-R} - 0\right) = -\frac{\mu_l - 1}{R}$। যৌথ লেন্সের নতুন ফোকাস দূরত্ব $F$ মাপলে: $\frac{1}{F} = \frac{1}{f_1} + \frac{1}{f_l} \implies \frac{1}{f_l} = \frac{1}{F} - \frac{1}{f_1}$। অতএব তরলের প্রতিসরাঙ্ক $\mu_l = 1 + \frac{R}{|f_l|}$।</t>
@@ -3571,11 +3346,6 @@
           <t>একটি উত্তল লেন্সের কেন্দ্রীয় বৃত্তাকার অর্ধেক ক্ষেত্রফল কালো কাগজ দিয়ে ঢেকে দেওয়া হলো। লেন্সের সামনে অবস্থিত বস্তুর প্রতিবিম্বের আকার, অবস্থান এবং উজ্জ্বলতার কী পরিবর্তন ঘটবে?</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>লেন্সের প্রতিটি ক্ষুদ্র অংশ সমগ্র বস্তুর পূর্ণ প্রতিবিম্ব তৈরি করতে সক্ষম। কেন্দ্র ঢেকে দিলেও লেন্সের উন্মুক্ত প্রান্তীয় বলয়াকার অংশ দিয়ে প্রতিসৃত রশ্মিগুলো যথারীতি সঠিক ফোকাস দূরত্ব ও জ্যামিতিক অবস্থানে মিলিত হয়। ফলে লেন্সের সমীকরণ $\frac{1}{v} - \frac{1}{u} = \frac{1}{f}$ অপরিবর্তিত থাকায় প্রতিবিম্বের অবস্থান এবং বিবর্ধন $m = v/u$ হুবহু একই থাকে। তবে লেন্সে প্রবেশকারী মোট আলোক ফ্লাক্স লেন্সের উন্মুক্ত ক্ষেত্রফলের সমানুপাতিক: $\Phi \propto A_{\text{open}} = A_{\text{total}} - A_{\text{covered}} = A/2$। ফলে প্রতিবিম্বে প্রতি সেকেন্ডে আপতিত আলোক শক্তির পরিমাণ অর্ধেক হয়ে যাওয়ায় প্রতিবিম্বটি আগের তুলনায় আবছা বা ৫০% কম উজ্জ্বল দেখাবে।</t>
@@ -3621,11 +3391,6 @@
           <t>মোটা লেন্স বা ব্যবধানে থাকা দুটি পাতলা লেন্সের ক্ষেত্রে ছয়টি কার্ডিনাল বিন্দু (Cardinal Points: দুটি ফোকাল পয়েন্ট, দুটি প্রিন্সিপাল পয়েন্ট এবং দুটি নোডাল পয়েন্ট)-এর তাৎপর্য কী? লেন্সের উভয়পাশের মাধ্যম একই হলে নোডাল পয়েন্ট ও প্রিন্সিপাল পয়েন্টের অবস্থান কেমন হয়?</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>কার্ল ফ্রিডরিখ গাউস প্রমাণ করেন যে যেকোনো জটিল কোঅ্যাক্সিয়াল অপটিক্যাল সিস্টেমকে ৬টি কার্ডিনাল বিন্দুর সাহায্যে উপস্থাপন করা যায়: (১) দুটি ফোকাস বিন্দু ($F_1, F_2$): যেখান থেকে আলো সমান্তরাল হয় বা সমান্তরাল আলো মিলিত হয়। (২) দুটি প্রধান বিন্দু ($H_1, H_2$): যেখান থেকে সমবায়ের ফোকাস দূরত্ব ও বস্তুর দূরত্ব মাপা হয় এবং যাদের তলদ্বয়ের মাঝে একক ধনাত্মক বিবর্ধন ($m = +1$) থাকে। (৩) দুটি নোডাল বিন্দু ($N_1, N_2$): যে বিন্দুদ্বয় বরাবর আপতিত রশ্মি কোনো কৌণিক বিচ্যুতি ছাড়া নির্গত হয় (কৌণিক বিবর্ধন $+1$)। যদি অপটিক্যাল সিস্টেমের প্রবেশ মাধ্যম এবং নির্গমন মাধ্যম একই হয় (যেমন উভয়পাশে বাতাস), তবে নোডাল বিন্দুগুলো হুবহু প্রিন্সিপাল বিন্দুগুলোর সাথে মিলে যায় ($N_1 \equiv H_1$ এবং $N_2 \equiv H_2$)।</t>
@@ -3655,12 +3420,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>প্রিজমের ন্যূনতম বিচ্যুতি ও প্রতিসরাঙ্ক</t>
+          <t>প্রতিসরণ, সংকট কোণ ও প্রিজম বিচ্যুতি (Refraction, Prism &amp; Dispersion)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -3668,30 +3433,25 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##
-$A = 60^\circ$ প্রতিসারক কোণবিশিষ্ট একটি সমবাহু কাচ প্রিজমে আলো প্রতিসরিত হয়ে ন্যূনতম বিচ্যুতি $\delta_m = 38^\circ$ প্রদর্শন করে। প্রিজমটির উপাদানের প্রতিসরাঙ্ক $\mu$ এবং এর পৃষ্ঠে আপতন কোণ $i_1$ কত?</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+পানিতে আলোর বেগ $2.25 \times 10^8\text{ m/s}$ এবং কাচে আলোর বেগ $2.0 \times 10^8\text{ m/s}$। বায়ুর সাপেক্ষে পানি ও কাচের প্রতিসরাঙ্ক নির্ণয় কর। কাচ হতে পানিতে আলোর প্রতিসরণের ক্ষেত্রে সংকট কোণ $\theta_c$ কত? ($c = 3.0 \times 10^8\text{ m/s}$)।</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>প্রতিসরাঙ্কের সূত্র: $\mu = \frac{\sin\left(\frac{A + \delta_m}{2}\right)}{\sin\left(\frac{A}{2}\right)} = \frac{\sin\left(\frac{60^\circ + 38^\circ}{2}\right)}{\sin(30^\circ)} = \frac{\sin(49^\circ)}{0.5} = \frac{0.7547}{0.5} \approx 1.509$।
-আপতন কোণ $i_1 = \frac{A + \delta_m}{2} = \frac{60^\circ + 38^\circ}{2} = 49^\circ$।</t>
+          <t>প্রতিসরাঙ্ক $n = \frac{c}{v}$। পানির $n_w = \frac{3.0 \times 10^8}{2.25 \times 10^8} = 1.333$। কাচের $n_g = \frac{3.0 \times 10^8}{2.0 \times 10^8} = 1.50$। কাচ হতে পানিতে সংকট কোণ: $\sin\theta_c = \frac{n_w}{n_g} = \frac{1.333}{1.50} = \frac{4/3}{3/2} = \frac{8}{9} \approx 0.8889$। সংকট কোণ $\theta_c = \arcsin(8/9) \approx 62.73^\circ$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>$\mu = 1.516$, আপতন কোণ $i_1 = 49^\circ$</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>$n_{\text{water}} = 1.333, n_{\text{glass}} = 1.50$, সংকট কোণ $\theta_c = 62.73^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3711,7 +3471,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 2</t>
+          <t>প্রতিসরণ, সংকট কোণ ও প্রিজম বিচ্যুতি (Refraction, Prism &amp; Dispersion)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3720,29 +3480,29 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 14\text{ cm}$। লেন্স হতে $39\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি সুইমিং পুলের তলদেশে একটি ক্ষুদ্র বাল্ব রাখা আছে। পানির গভীরতা $h = 2.0\text{ m}$ এবং পানির প্রতিসরাঙ্ক $n = rac{4}{3}$। পৃষ্ঠের ওপর যে বৃত্তাকার ক্ষেত্রফল দিয়ে আলো নির্গত হবে তার ব্যাসার্ধ $R$ এবং ক্ষেত্রফল কত?</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-39} = \frac{1}{14} \implies v = 21.84\text{ cm}$।
-বিবর্ধন $m = |v/u| = 21.84/39 = 0.56$।</t>
+          <t>সংকট কোণে আলো তল স্পর্শ করে: $\sin\theta_c = \frac{1}{n} = \frac{3}{4}$। $\tan\theta_c = \frac{\sin\theta_c}{\cos\theta_c} = \frac{3/4}{\sqrt{1 - 9/16}} = \frac{3}{\sqrt{7}}$। বৃত্তের ব্যাসার্ধ $R = h\tan\theta_c = \frac{2.0 \times 3}{\sqrt{7}} = \frac{6}{\sqrt{7}} \approx 2.2678\text{ m}$। নির্গমন ক্ষেত্রফল $A = \pi R^2 = \pi \left(\frac{36}{7}\right) \approx 16.157\text{ m}^2$।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>$v = 21.84\text{ cm}, m = 0.56$</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>বৃত্তের ব্যাসার্ধ $R = 2.268\text{ m}$, ক্ষেত্রফল $A = 16.16\text{ m}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3762,7 +3522,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 3</t>
+          <t>প্রতিসরণ, সংকট কোণ ও প্রিজম বিচ্যুতি (Refraction, Prism &amp; Dispersion)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3771,29 +3531,29 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 16\text{ cm}$। লেন্স হতে $41\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি কাচের স্ল্যাবের ($n = 1.50$) প্রকৃত বেধ $t = 9.0\text{ cm}$। উপর হতে খাড়া নিচের দিকে তাকালে স্ল্যাবের তলদেশের একটি দাগ কত উপরে দৃশ্যমান হবে (আপাত সরণ বা Normal shift $\Delta t$) এবং আপাত বেধ $d'$ কত?</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-41} = \frac{1}{16} \implies v = 26.24\text{ cm}$।
-বিবর্ধন $m = |v/u| = 26.24/41 = 0.64$।</t>
+          <t>আপাত গভীরতা $d' = \frac{t}{n} = \frac{9.0\text{ cm}}{1.50} = 6.0\text{ cm}$। আপাত সরণ $\Delta t = t - d' = t\left(1 - \frac{1}{n}\right) = 9.0\left(1 - \frac{1}{1.5}\right) = 9.0 \times \frac{1}{3} = 3.0\text{ cm}$।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>$v = 26.24\text{ cm}, m = 0.64$</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>আপাত বেধ $d' = 6.0\text{ cm}$, দাগটি $\Delta t = 3.0\text{ cm}$ উপরে উঠবে</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3813,7 +3573,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 4</t>
+          <t>প্রতিসরণ, সংকট কোণ ও প্রিজম বিচ্যুতি (Refraction, Prism &amp; Dispersion)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3822,34 +3582,29 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##
-একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 18\text{ cm}$। লেন্স হতে $43\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+একটি অপটিক্যাল ফাইবারের কোরের প্রতিসরাঙ্ক $n_1 = 1.50$ এবং ক্ল্যাডিংয়ের প্রতিসরাঙ্ক $n_2 = 1.45$। ফাইবারের সংকট কোণ $\theta_c$ এবং বায়ুতে গ্রহণযোগ্যতার সর্বোচ্চ শঙ্কু কোণ (Acceptance angle $\theta_a$) নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##</t>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-43} = \frac{1}{18} \implies v = 30.96\text{ cm}$।
-বিবর্ধন $m = |v/u| = 30.96/43 = 0.72$।</t>
+          <t>সংকট কোণ $\sin\theta_c = \frac{n_2}{n_1} = \frac{1.45}{1.50} \approx 0.9667 \implies \theta_c \approx 75.16^\circ$। নিউমেরিক্যাল অ্যাপারচার $NA = \sqrt{n_1^2 - n_2^2} = \sqrt{1.50^2 - 1.45^2} = \sqrt{2.25 - 2.1025} = \sqrt{0.1475} \approx 0.384$। গ্রহণযোগ্যতা কোণ $\sin\theta_a = NA = 0.384 \implies \theta_a = \arcsin(0.384) \approx 22.59^\circ \approx 22.6^\circ$।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>$v = 30.96\text{ cm}, m = 0.72$</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>সংকট কোণ $\theta_c = 75.16^\circ$, গ্রহণযোগ্যতা কোণ $\theta_a = 22.60^\circ$ (Numerical Aperture $NA = 0.384$)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3869,7 +3624,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 5</t>
+          <t>প্রতিসরণ, সংকট কোণ ও প্রিজম বিচ্যুতি (Refraction, Prism &amp; Dispersion)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3878,29 +3633,29 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 20\text{ cm}$। লেন্স হতে $45\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি আলোক রশ্মি বাতাস হতে কাচে ($n = 1.50$) আপতিত হলো। আপতন কোণ কত হলে প্রতিফলিত রশ্মি এবং প্রতিসরিত রশ্মি পরস্পরের ওপর সমকোণে ($90^\circ$) অবস্থান করবে? (ব্রুস্টারের কোণ নির্ণয় কর)।</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-45} = \frac{1}{20} \implies v = 36.0\text{ cm}$।
-বিবর্ধন $m = |v/u| = 36.0/45 = 0.8$।</t>
+          <t>প্রতিফলিত ও প্রতিসরিত রশ্মি লম্ব হলে ব্রুস্টারের সূত্র প্রযোজ্য: $\tan\theta_p = n = 1.50 \implies \theta_p = \arctan(1.50) \approx 56.31^\circ$।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>$v = 36.0\text{ cm}, m = 0.8$</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>আপতন কোণ $\theta_p = 56.31^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3920,7 +3675,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 6</t>
+          <t>প্রতিসরণ, সংকট কোণ ও প্রিজম বিচ্যুতি (Refraction, Prism &amp; Dispersion)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3929,29 +3684,29 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 22\text{ cm}$। লেন্স হতে $47\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+একটি ট্যাংকে $8.0\text{ cm}$ গভীর পানি ($n = 4/3$) এবং তার ওপরে $6.0\text{ cm}$ গভীর তেল ($n = 1.50$) রয়েছে। উপর হতে খাড়াভাবে তাকালে ট্যাংকের তলদেশের আপাত গভীরতা কত দেখাবে?</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-47} = \frac{1}{22} \implies v = 41.36\text{ cm}$।
-বিবর্ধন $m = |v/u| = 41.36/47 = 0.88$।</t>
+          <t>মোট আপাত গভীরতা হলো পৃথক আপাত গভীরতার সমষ্টি: $d' = \frac{d_1}{n_1} + \frac{d_2}{n_2} = \frac{8.0}{4/3} + \frac{6.0}{1.50} = \left(8.0 \times \frac{3}{4}\right) + 4.0 = 6.0 + 4.0 = 10.0\text{ cm}$ (প্রকৃত গভীরতা $14\text{ cm}$ ছিল)।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>$v = 41.36\text{ cm}, m = 0.88$</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>আপাত মোট গভীরতা $d' = 10.0\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3971,7 +3726,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 7</t>
+          <t>প্রতিসরণ, সংকট কোণ ও প্রিজম বিচ্যুতি (Refraction, Prism &amp; Dispersion)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3980,29 +3735,29 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 24\text{ cm}$। লেন্স হতে $49\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##GEO:triangle[b=3,h=3][size:small]##
+একটি সমবাহু প্রিজমের প্রতিসরাঙ্ক $n = 1.50$। প্রিজমটির ন্যূনতম বিচ্যুতি কোণ $\delta_m$ নির্ণয় কর। ($A = 60^\circ$)।</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[b=3,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-49} = \frac{1}{24} \implies v = 47.04\text{ cm}$।
-বিবর্ধন $m = |v/u| = 47.04/49 = 0.96$।</t>
+          <t>প্রিজম সূত্র: $n = \frac{\sin(\frac{A + \delta_m}{2})}{\sin(A/2)} \implies 1.50 = \frac{\sin(\frac{60^\circ + \delta_m}{2})}{\sin 30^\circ} = \frac{\sin(30^\circ + \delta_m/2)}{0.5} \implies \sin(30^\circ + \delta_m/2) = 0.75$। $30^\circ + \delta_m/2 = \arcsin(0.75) \approx 48.59^\circ \implies \delta_m/2 = 18.59^\circ \implies \delta_m = 37.18^\circ$।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>$v = 47.04\text{ cm}, m = 0.96$</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>ন্যূনতম বিচ্যুতি কোণ $\delta_m = 37.18^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4022,7 +3777,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 8</t>
+          <t>প্রতিসরণ, সংকট কোণ ও প্রিজম বিচ্যুতি (Refraction, Prism &amp; Dispersion)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4031,34 +3786,29 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##
-একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 26\text{ cm}$। লেন্স হতে $51\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
+          <t>##GEO:triangle[b=3,h=3][size:small]##
+একটি সরু প্রিজমের প্রতিসারক কোণ $A = 5.0^\circ$ এবং এর উপাদানের প্রতিসরাঙ্ক $n = 1.52$। প্রিজমটি দ্বারা সৃষ্ট বিচ্যুতির কোণ $\delta$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##</t>
+          <t>##GEO:triangle[b=3,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-51} = \frac{1}{26} \implies v = 53.04\text{ cm}$।
-বিবর্ধন $m = |v/u| = 53.04/51 = 1.04$।</t>
+          <t>সরু প্রিজমের বিচ্যুতি: $\delta = (n - 1)A = (1.52 - 1) \times 5.0^\circ = 0.52 \times 5.0^\circ = 2.60^\circ$।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>$v = 53.04\text{ cm}, m = 1.04$</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>বিচ্যুতি কোণ $\delta = 2.60^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4078,7 +3828,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 9</t>
+          <t>প্রতিসরণ, সংকট কোণ ও প্রিজম বিচ্যুতি (Refraction, Prism &amp; Dispersion)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4087,29 +3837,29 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 28\text{ cm}$। লেন্স হতে $53\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>##GEO:triangle[b=3,h=3][size:small]##
+একটি প্রিজমের উপাদানের লাল ও বেগুনি আলোর প্রতিসরাঙ্ক যথাক্রমে $n_r = 1.62$ এবং $n_v = 1.66$। প্রিজমের কোণ $A = 6^\circ$ হলে কৌণিক বিচ্ছুরণ (Angular dispersion $	heta$) এবং বিচ্ছুরণ ক্ষমতা (Dispersive power $\omega$) নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[b=3,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-53} = \frac{1}{28} \implies v = 59.36\text{ cm}$।
-বিবর্ধন $m = |v/u| = 59.36/53 = 1.12$।</t>
+          <t>গড় প্রতিসরাঙ্ক $n_y = \frac{n_v + n_r}{2} = \frac{1.66 + 1.62}{2} = 1.64$। কৌণিক বিচ্ছুরণ $\theta = (n_v - n_r)A = (1.66 - 1.62) \times 6^\circ = 0.04 \times 6^\circ = 0.24^\circ$। বিচ্ছুরণ ক্ষমতা $\omega = \frac{n_v - n_r}{n_y - 1} = \frac{0.04}{1.64 - 1} = \frac{0.04}{0.64} = \frac{1}{16} = 0.0625$।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>$v = 59.36\text{ cm}, m = 1.12$</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>কৌণিক বিচ্ছুরণ $\theta = 0.24^\circ$, বিচ্ছুরণ ক্ষমতা $\omega = 0.0625 = \frac{1}{16}$</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4129,7 +3879,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 10</t>
+          <t>প্রতিসরণ, সংকট কোণ ও প্রিজম বিচ্যুতি (Refraction, Prism &amp; Dispersion)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,29 +3888,29 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 10\text{ cm}$। লেন্স হতে $55\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+পূর্ণ অভ্যন্তরীণ প্রতিফলনের দুটি আবশ্যকীয় শর্ত কী কী এবং কেন অপটিক্যাল ফাইবারে আলোক সংকেত কোনো শক্তির অপচয় ছাড়াই দীর্ঘ দূরত্ব অতিক্রম করতে পারে?</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-55} = \frac{1}{10} \implies v = 12.22\text{ cm}$।
-বিবর্ধন $m = |v/u| = 12.22/55 = 0.22$।</t>
+          <t>সাধারণ দর্পণে রূপালি প্রলেপে ১০-২০% আলো শোষিত হয়। কিন্তু পূর্ণ অভ্যন্তরীণ প্রতিফলনে আলো ১০০% নিখুঁতভাবে কোরের ভেতর সম্পূর্ণ প্রতিফলিত হয়, কোনো শক্তি শোষিত বা বাইরে নির্গত হয় না। ফলে অপটিক্যাল ফাইবারে সিগন্যাল প্রায় অবিকৃত অবস্থায় দীর্ঘ দূরত্ব অতিক্রম করতে পারে।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>$v = 12.22\text{ cm}, m = 0.22$</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>শর্ত: (১) আলো ঘন মাধ্যম হতে লঘু মাধ্যমে আপতিত হতে হবে, (২) আপতন কোণ সংকট কোণের চেয়ে বড় হতে হবে ($\theta &gt; \theta_c$); পূর্ণ প্রতিফলনে কোনো আলো প্রতিসরিত হয়ে অপচয় হয় না</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4180,38 +3930,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 11</t>
+          <t>লেন্স প্রস্তুতকারকের সূত্র ও লেন্স সমবায় (Lenses &amp; Combinations)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 12\text{ cm}$। লেন্স হতে $57\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি উভোত্তল লেন্সের দুই তলের বক্রতার ব্যাসার্ধ যথাক্রমে $R_1 = 20.0\text{ cm}$ এবং $R_2 = 30.0\text{ cm}$। কাচের প্রতিসরাঙ্ক $n_g = 1.50$ হলে বায়ুতে লেন্সটির ফোকাস দূরত্ব কত? লেন্সটির ক্ষমতা $P$ ডায়োপ্টারে নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-57} = \frac{1}{12} \implies v = 15.2\text{ cm}$।
-বিবর্ধন $m = |v/u| = 15.2/57 = 0.27$।</t>
+          <t>লেন্স প্রস্তুতকারকের সূত্র: $\frac{1}{f} = (n - 1)\left(\frac{1}{R_1} - \frac{1}{R_2}\right)$। চিহ্ন নীতি অনুসারে উভোত্তলে $R_1 = +20\text{ cm}, R_2 = -30\text{ cm}$। $\frac{1}{f} = (1.50 - 1)\left(\frac{1}{20} - \left(-\frac{1}{30}\right)\right) = 0.50\left(\frac{3 + 2}{60}\right) = 0.50 \times \frac{5}{60} = \frac{2.5}{60} = \frac{1}{24} \implies f = 24.0\text{ cm} = 0.24\text{ m}$। লেন্সের ক্ষমতা $P = \frac{1}{f(\text{m})} = \frac{1}{0.24} \approx +4.167\text{ D}$।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>$v = 15.2\text{ cm}, m = 0.27$</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>ফোকাস দূরত্ব $f = +24.0\text{ cm} = 0.24\text{ m}$, ক্ষমতা $P = +4.17\text{ D}$</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4231,43 +3981,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 12</t>
+          <t>লেন্স প্রস্তুতকারকের সূত্র ও লেন্স সমবায় (Lenses &amp; Combinations)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##
-একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 14\text{ cm}$। লেন্স হতে $59\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+উপরের উভোত্তল লেন্সটিকে ($f_a = 24.0\text{ cm}$) পানিতে ($n_w = 4/3$) নিমজ্জিত করলে পানিতে এর ফোকাস দূরত্ব $f_w$ কত হবে?</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-59} = \frac{1}{14} \implies v = 18.36\text{ cm}$।
-বিবর্ধন $m = |v/u| = 18.36/59 = 0.31$।</t>
+          <t>তরলে ফোকাস দূরত্ব: $\frac{f_l}{f_a} = \frac{n_g - 1}{\frac{n_g}{n_l} - 1} = \frac{1.50 - 1}{\frac{1.50}{4/3} - 1} = \frac{0.50}{\frac{9}{8} - 1} = \frac{0.50}{1/8} = 0.50 \times 8 = 4.0$। অতএব $f_w = 4.0 \times f_a = 4.0 \times 24.0\text{ cm} = +96.0\text{ cm}$।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>$v = 18.36\text{ cm}, m = 0.31$</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>পানিতে ফোকাস দূরত্ব $f_w = +96.0\text{ cm}$ ($4.0$ গুণ বৃদ্ধি পাবে)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4287,38 +4032,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 13</t>
+          <t>লেন্স প্রস্তুতকারকের সূত্র ও লেন্স সমবায় (Lenses &amp; Combinations)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 16\text{ cm}$। লেন্স হতে $61\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি উত্তল লেন্স হতে $30.0\text{ cm}$ দূরে একটি বস্তু রাখায় লেন্সের অপর পাশে $60.0\text{ cm}$ দূরে একটি বাস্তব প্রতিবিম্ব গঠিত হয়। লেন্সটির ফোকাস দূরত্ব $f$ এবং রৈখিক বিবর্ধন $m$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-61} = \frac{1}{16} \implies v = 21.69\text{ cm}$।
-বিবর্ধন $m = |v/u| = 21.69/61 = 0.36$।</t>
+          <t>চিহ্ন নীতি: বস্তু দূরত্ব $u = -30.0\text{ cm}$, বাস্তব বিম্ব দূরত্ব $v = +60.0\text{ cm}$। লেন্স সমীকরণ: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{60} - \left(-\frac{1}{30}\right) = \frac{1}{f} \implies \frac{1}{60} + \frac{2}{60} = \frac{3}{60} = \frac{1}{20} \implies f = +20.0\text{ cm}$। বিবর্ধন $m = \frac{v}{u} = \frac{60}{-30} = -2.0$ (বিম্ব বাস্তব ও উল্টা এবং আকারের দ্বিগুণ)।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>$v = 21.69\text{ cm}, m = 0.36$</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>ফোকাস দূরত্ব $f = +20.0\text{ cm}$, বিবর্ধন $m = -2.0$</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4338,38 +4083,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 14</t>
+          <t>লেন্স প্রস্তুতকারকের সূত্র ও লেন্স সমবায় (Lenses &amp; Combinations)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 18\text{ cm}$। লেন্স হতে $63\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+দুটি পাতলা লেন্স যাদের ক্ষমতা যথাক্রমে $P_1 = +5.0\text{ D}$ এবং $P_2 = -2.0\text{ D}$, পরস্পরের সংস্পর্শে রাখা হলো। সমবায়টির তুল্য ক্ষমতা $P$, তুল্য ফোকাস দূরত্ব $F$ এবং এটি অভিসারী না অপসারী লেন্সের মতো আচরণ করবে?</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-63} = \frac{1}{18} \implies v = 25.2\text{ cm}$।
-বিবর্ধন $m = |v/u| = 25.2/63 = 0.4$।</t>
+          <t>সংস্পর্শে তুল্য ক্ষমতা $P = P_1 + P_2 = +5.0 + (-2.0) = +3.0\text{ D}$। তুল্য ফোকাস দূরত্ব $F = \frac{1}{P} = \frac{1}{+3.0}\text{ m} = \frac{100}{3}\text{ cm} \approx +33.33\text{ cm}$। ক্ষমতা ধনাত্মক হওয়ায় সমবায়টি একটি উত্তল বা অভিসারী লেন্সের ন্যায় আচরণ করবে।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>$v = 25.2\text{ cm}, m = 0.4$</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>তুল্য ক্ষমতা $P = +3.0\text{ D}$, তুল্য ফোকাস $F = +33.33\text{ cm}$ (অভিসারী লেন্স)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4389,38 +4134,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 15</t>
+          <t>লেন্স প্রস্তুতকারকের সূত্র ও লেন্স সমবায় (Lenses &amp; Combinations)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 20\text{ cm}$। লেন্স হতে $65\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি সমতল-উত্তল (Plano-convex) লেন্সের বক্রতলের ব্যাসার্ধ $R = 15.0\text{ cm}$ এবং প্রতিসরাঙ্ক $n = 1.50$। লেন্সটির ফোকাস দূরত্ব কত? যদি এর সমতল পৃষ্ঠটিতে রুপার প্রলেপ (Silvering) দেওয়া হয়, তবে সমবায়টি কত ফোকাস দূরত্বের অবতল দর্পণে পরিণত হবে?</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-65} = \frac{1}{20} \implies v = 28.89\text{ cm}$।
-বিবর্ধন $m = |v/u| = 28.89/65 = 0.44$।</t>
+          <t>লেন্স মেকার: $\frac{1}{f} = (n - 1)\left(\frac{1}{R} - \frac{1}{\infty}\right) = (1.5 - 1)\frac{1}{15} = \frac{0.5}{15} = \frac{1}{30} \implies f = 30.0\text{ cm}$। সমতল পৃষ্ঠে রূপা দিলে সমবায় ক্ষমতা $P_{\text{eq}} = 2 P_L + P_M = 2\left(\frac{1}{f}\right) + 0 = \frac{2}{f} = \frac{2}{30} = \frac{1}{15}\text{ cm}^{-1}$। সমতুল্য দর্পণের ফোকাস $F = -\frac{1}{P_{\text{eq}}} = -15.0\text{ cm}$ (অবতল দর্পণ)।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>$v = 28.89\text{ cm}, m = 0.44$</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>লেন্সের ফোকাস $f = +30.0\text{ cm}$, রূপালী সমতল-উত্তল দর্পণের ফোকাস $F = -15.0\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4440,43 +4185,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 16</t>
+          <t>লেন্স প্রস্তুতকারকের সূত্র ও লেন্স সমবায় (Lenses &amp; Combinations)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##
-একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 22\text{ cm}$। লেন্স হতে $67\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি অবতল লেন্সের ফোকাস দূরত্ব $f = 20.0\text{ cm}$। লেন্সটি হতে কত দূরে একটি বস্তু রাখলে এর অবাস্তব প্রতিবিম্ব বস্তুর আকারের এক-তৃতীয়াংশ ($m = +1/3$) হবে?</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-67} = \frac{1}{22} \implies v = 32.76\text{ cm}$।
-বিবর্ধন $m = |v/u| = 32.76/67 = 0.49$।</t>
+          <t>অবতল লেন্সে $f = -20.0\text{ cm}$। বিবর্ধন $m = \frac{v}{u} = \frac{1}{3} \implies v = \frac{u}{3}$। লেন্স সমীকরণ: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{3}{u} - \frac{1}{u} = \frac{1}{-20} \implies \frac{2}{u} = -\frac{1}{20} \implies u = -40.0\text{ cm}$।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>$v = 32.76\text{ cm}, m = 0.49$</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>বস্তু দূরত্ব $u = -40.0\text{ cm}$ (লেন্স হতে $40.0\text{ cm}$ সামনে)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4496,38 +4236,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 17</t>
+          <t>লেন্স প্রস্তুতকারকের সূত্র ও লেন্স সমবায় (Lenses &amp; Combinations)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 24\text{ cm}$। লেন্স হতে $69\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=2.5][size:small]##
+একটি পর্দায় একটি উজ্জ্বল বিন্দুর স্পষ্ট প্রতিবিম্ব ফেলার জন্য একটি উত্তল লেন্সের দুটি অবস্থানের মধ্যবর্তী ব্যবধান $d = 20.0\text{ cm}$ পাওয়া গেল। বস্তু ও পর্দার মোট দূরত্ব $D = 100.0\text{ cm}$ হলে লেন্সটির ফোকাস দূরত্ব $f$ কত? (স্থানচ্যুতি পদ্ধতি / Displacement method)।</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-69} = \frac{1}{24} \implies v = 36.8\text{ cm}$।
-বিবর্ধন $m = |v/u| = 36.8/69 = 0.53$।</t>
+          <t>স্থানচ্যুতি পদ্ধতিতে ফোকাস দূরত্বের সমীকরণ: $f = \frac{D^2 - d^2}{4D}$। মান বসিয়ে: $f = \frac{100^2 - 20^2}{4(100)} = \frac{10000 - 400}{400} = \frac{9600}{400} = 24.0\text{ cm}$।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>$v = 36.8\text{ cm}, m = 0.53$</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>ফোকাস দূরত্ব $f = 24.0\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4547,38 +4287,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 18</t>
+          <t>লেন্স প্রস্তুতকারকের সূত্র ও লেন্স সমবায় (Lenses &amp; Combinations)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 26\text{ cm}$। লেন্স হতে $71\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি দ্বি-উত্তল কাচের লেন্সকে ($n = 1.50$) এমন একটি তরলে নিমজ্জিত করা হলো যার প্রতিসরাঙ্ক কাচের চেয়ে বেশি ($n_l = 1.65$)। লেন্সটির আচরণে কী পরিবর্তন ঘটবে?</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-71} = \frac{1}{26} \implies v = 41.02\text{ cm}$।
-বিবর্ধন $m = |v/u| = 41.02/71 = 0.58$।</t>
+          <t>লেন্স প্রস্তুতকারক সূত্রে: $\frac{1}{f_l} = \left(\frac{n_g}{n_l} - 1\right)\left(\frac{1}{R_1} - \frac{1}{R_2}\right)$। যেহেতু $n_l &gt; n_g$, তাই $\left(\frac{n_g}{n_l} - 1\right) &lt; 0$ (ঋণাত্মক)। ফলে উত্তল লেন্সের স্বাভাবিক ধনাত্মক ফোকাস দূরত্ব উল্টে ঋণাত্মক হয়ে যায় এবং এটি আলো কেন্দ্রীভূত না করে অপসারী করে।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>$v = 41.02\text{ cm}, m = 0.58$</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>উত্তল লেন্সটি অবতল বা অপসারী (Diverging) লেন্সের ন্যায় আচরণ করবে</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4598,38 +4338,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 19</t>
+          <t>লেন্স প্রস্তুতকারকের সূত্র ও লেন্স সমবায় (Lenses &amp; Combinations)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 28\text{ cm}$। লেন্স হতে $73\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি বস্তুর বাস্তব প্রতিবিম্ব উত্তল লেন্স দ্বারা পর্দায় গঠিত হতে হলে বস্তু ও পর্দার মধ্যবর্তী ন্যূনতম দূরত্ব কত হতে হবে?</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-73} = \frac{1}{28} \implies v = 45.42\text{ cm}$।
-বিবর্ধন $m = |v/u| = 45.42/73 = 0.62$।</t>
+          <t>স্থানচ্যুতি পদ্ধতি অনুসারে $D^2 - 4Df = d^2 \ge 0 \implies D(D - 4f) \ge 0 \implies D \ge 4f$। সুতরাং বাস্তব বিম্ব পর্দায় পাওয়ার জন্য বস্তু ও পর্দার ব্যবধান ন্যূনতম $4f$ হতে হবে।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>$v = 45.42\text{ cm}, m = 0.62$</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>ন্যূনতম দূরত্ব $D_{\min} = 4 f$</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4649,43 +4389,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 20</t>
+          <t>লেন্স প্রস্তুতকারকের সূত্র ও লেন্স সমবায় (Lenses &amp; Combinations)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##
-একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 10\text{ cm}$। লেন্স হতে $75\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+দুটি উত্তল লেন্স যাদের ফোকাস দূরত্ব যথাক্রমে $f_1 = 20.0\text{ cm}$ এবং $f_2 = 10.0\text{ cm}$, পরস্পর হতে $d = 5.0\text{ cm}$ দূরত্বে অবস্থিত। সমবায়টির তুল্য ফোকাস দূরত্ব $F$ কত?</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-75} = \frac{1}{10} \implies v = 11.54\text{ cm}$।
-বিবর্ধন $m = |v/u| = 11.54/75 = 0.15$।</t>
+          <t>ব্যবধানযুক্ত লেন্সের তুল্য ফোকাস সূত্র: $\frac{1}{F} = \frac{1}{f_1} + \frac{1}{f_2} - \frac{d}{f_1 f_2} = \frac{1}{20} + \frac{1}{10} - \frac{5}{20 \times 10} = \frac{1}{20} + \frac{2}{20} - \frac{5}{200} = \frac{3}{20} - \frac{1}{40} = \frac{6 - 1}{40} = \frac{5}{40} = \frac{1}{8} \implies F = 8.0\text{ cm}$।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>$v = 11.54\text{ cm}, m = 0.15$</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>তুল্য ফোকাস দূরত্ব $F = 8.0\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4705,38 +4440,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 21</t>
+          <t>আলোকীয় যন্ত্রাদি ও দৃষ্টির ত্রুটি (Microscopes, Telescopes &amp; Eye Defects)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 12\text{ cm}$। লেন্স হতে $77\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি সরল অণুবীক্ষণ যন্ত্রে $f = 5.0\text{ cm}$ ফোকাস দূরত্বের একটি উত্তল লেন্স ব্যবহার করা হয়েছে। স্পষ্ট দর্শনের ন্যূনতম দূরত্ব $D = 25.0\text{ cm}$ হলে: (ক) স্পষ্ট দর্শনের নিকট বিন্দুতে এবং (খ) অসীম দূরত্বে ফোকাসিংয়ের ক্ষেত্রে লেন্সটির বিবর্ধন ক্ষমতা কত?</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-77} = \frac{1}{12} \implies v = 14.22\text{ cm}$।
-বিবর্ধন $m = |v/u| = 14.22/77 = 0.18$।</t>
+          <t>(ক) নিকট বিন্দুতে বিবর্ধন: $M = 1 + \frac{D}{f} = 1 + \frac{25}{5} = 1 + 5 = 6.0$। (খ) স্বাভাবিক বা অসীম দর্শনে বিবর্ধন: $M_\infty = \frac{D}{f} = \frac{25}{5} = 5.0$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>$v = 14.22\text{ cm}, m = 0.18$</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(ক) নিকট বিন্দুতে বিবর্ধন $M = 6.0$, (খ) অসীমে বিবর্ধন $M_\infty = 5.0$</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4756,38 +4491,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 22</t>
+          <t>আলোকীয় যন্ত্রাদি ও দৃষ্টির ত্রুটি (Microscopes, Telescopes &amp; Eye Defects)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 14\text{ cm}$। লেন্স হতে $79\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+একটি যৌগিক অণুবীক্ষণ যন্ত্রের অভিলক্ষ্যের (Objective) ফোকাস দূরত্ব $f_o = 1.0\text{ cm}$ এবং অভিনেত্রের (Eyepiece) ফোকাস দূরত্ব $f_e = 5.0\text{ cm}$। অভিলক্ষ্য হতে $u_o = 1.1\text{ cm}$ দূরে একটি বস্তু স্থাপন করা হলো। স্পষ্ট দর্শনের ন্যূনতম দূরত্ব $D = 25.0\text{ cm}$-এ বিম্ব গঠিত হলে অণুবীক্ষণ যন্ত্রটির মোট বিবর্ধন $M$ এবং নলের দৈর্ঘ্য $L$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-79} = \frac{1}{14} \implies v = 17.02\text{ cm}$।
-বিবর্ধন $m = |v/u| = 17.02/79 = 0.22$।</t>
+          <t>অভিলক্ষ্যের ক্ষেত্রে: $\frac{1}{v_o} - \frac{1}{-1.1} = \frac{1}{1.0} \implies \frac{1}{v_o} = 1 - \frac{10}{11} = \frac{1}{11} \implies v_o = 11.0\text{ cm}$। অভিলক্ষ্যের বিবর্ধন $m_o = \frac{v_o}{u_o} = \frac{11.0}{1.1} = 10.0$। অভিনেত্রের বিবর্ধন $m_e = 1 + \frac{D}{f_e} = 1 + \frac{25}{5} = 6.0$। মোট বিবর্ধন $M = m_o \times m_e = 10 \times 6 = 60.0$। অভিনেত্রের জন্য বস্তু দূরত্ব: $\frac{1}{-25} - \frac{1}{-u_e} = \frac{1}{5} \implies \frac{1}{u_e} = \frac{1}{5} + \frac{1}{25} = \frac{6}{25} \implies u_e = \frac{25}{6} \approx 4.167\text{ cm}$। নলের দৈর্ঘ্য $L = v_o + u_e = 11.0 + 4.167 = 15.167\text{ cm}$।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>$v = 17.02\text{ cm}, m = 0.22$</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>মোট বিবর্ধন $M = 60.0$, নলের দৈর্ঘ্য $L = 15.17\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4807,38 +4542,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 23</t>
+          <t>আলোকীয় যন্ত্রাদি ও দৃষ্টির ত্রুটি (Microscopes, Telescopes &amp; Eye Defects)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 16\text{ cm}$। লেন্স হতে $81\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4.5][size:small]##
+একটি নভো দূরবীক্ষণ যন্ত্রের অভিলক্ষ্য ও অভিনেত্রের ফোকাস দূরত্ব যথাক্রমে $f_o = 100.0\text{ cm}$ এবং $f_e = 5.0\text{ cm}$। স্বাভাবিক ফোকাসিংয়ে (Normal adjustment / অসীমে ফোকাসিং) দূরবীক্ষণ যন্ত্রটির কৌণিক বিবর্ধন $M$ এবং নলের দৈর্ঘ্য $L$ কত?</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-81} = \frac{1}{16} \implies v = 19.94\text{ cm}$।
-বিবর্ধন $m = |v/u| = 19.94/81 = 0.25$।</t>
+          <t>স্বাভাবিক ফোকাসিংয়ে কৌণিক বিবর্ধন $M = \frac{f_o}{f_e} = \frac{100.0}{5.0} = 20.0$। নলের দৈর্ঘ্য $L = f_o + f_e = 100.0 + 5.0 = 105.0\text{ cm}$।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>$v = 19.94\text{ cm}, m = 0.25$</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>বিবর্ধন $M = 20.0$, নলের দৈর্ঘ্য $L = 105.0\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4858,43 +4593,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 24</t>
+          <t>আলোকীয় যন্ত্রাদি ও দৃষ্টির ত্রুটি (Microscopes, Telescopes &amp; Eye Defects)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##
-একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 18\text{ cm}$। লেন্স হতে $83\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
+          <t>##GEO:cylinder[r=2,h=4.5][size:small]##
+উপরের দূরবীক্ষণ যন্ত্রটিতে স্পষ্ট দর্শনের নিকট বিন্দুতে ($D = 25.0\text{ cm}$) চূড়ান্ত বিম্ব গঠিত হলে বিবর্ধন $M'$ এবং নলের দৈর্ঘ্য $L'$ কত হবে?</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##</t>
+          <t>##GEO:cylinder[r=2,h=4.5][size:small]##</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-83} = \frac{1}{18} \implies v = 22.98\text{ cm}$।
-বিবর্ধন $m = |v/u| = 22.98/83 = 0.28$।</t>
+          <t>নিকট বিন্দুতে বিবর্ধন: $M' = \frac{f_o}{f_e}\left(1 + \frac{f_e}{D}\right) = \frac{100}{5}\left(1 + \frac{5}{25}\right) = 20(1 + 0.20) = 20 \times 1.20 = 24.0$। অভিনেত্রের বস্তু দূরত্ব $u_e = \frac{f_e D}{f_e + D} = \frac{5 \times 25}{30} = \frac{125}{30} \approx 4.167\text{ cm}$। নলের দৈর্ঘ্য $L' = f_o + u_e = 100 + 4.167 = 104.167\text{ cm}$।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>$v = 22.98\text{ cm}, m = 0.28$</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>বিবর্ধন $M' = 24.0$, নলের দৈর্ঘ্য $L' = 104.17\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4914,38 +4644,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 25</t>
+          <t>আলোকীয় যন্ত্রাদি ও দৃষ্টির ত্রুটি (Microscopes, Telescopes &amp; Eye Defects)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 20\text{ cm}$। লেন্স হতে $85\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4.5][size:small]##
+একটি জ্যোতির্বৈজ্ঞানিক দূরবীক্ষণ যন্ত্রের নলের দৈর্ঘ্য $L = 102.0\text{ cm}$ এবং এর বিবর্ধন ক্ষমতা $M = 50$ (স্বাভাবিক সমন্বয়ে)। অভিলক্ষ্য ও অভিনেত্রের ফোকাস দূরত্ব যথাক্রমে নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-85} = \frac{1}{20} \implies v = 26.15\text{ cm}$।
-বিবর্ধন $m = |v/u| = 26.15/85 = 0.31$।</t>
+          <t>স্বাভাবিক সমন্বয়ে $M = \frac{f_o}{f_e} = 50 \implies f_o = 50 f_e$। নলের দৈর্ঘ্য $L = f_o + f_e = 50 f_e + f_e = 51 f_e = 102.0\text{ cm} \implies f_e = \frac{102}{51} = 2.0\text{ cm}$। অভিলক্ষ্যের ফোকাস $f_o = 50(2.0) = 100.0\text{ cm}$।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>$v = 26.15\text{ cm}, m = 0.31$</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>অভিলক্ষ্যের ফোকাস $f_o = 100.0\text{ cm}$, অভিনেত্রের ফোকাস $f_e = 2.0\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4965,38 +4695,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 26</t>
+          <t>আলোকীয় যন্ত্রাদি ও দৃষ্টির ত্রুটি (Microscopes, Telescopes &amp; Eye Defects)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 22\text{ cm}$। লেন্স হতে $87\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+টেলিস্কোপের অভিলক্ষ্যের ব্যাস অনেক বড় করার বৈজ্ঞানিক কারণ কী? দেখাও যে এটি কেবল বেশি আলো সংগ্রহই করে না বরং কৌণিক বিভেদন সীমাও (Angular resolution limit $\theta = 1.22\lambda/D$) উন্নত করে।</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-87} = \frac{1}{22} \implies v = 29.45\text{ cm}$।
-বিবর্ধন $m = |v/u| = 29.45/87 = 0.34$।</t>
+          <t>অভিলক্ষ্যের ব্যাস $D$ বৃদ্ধি পেলে আলোর গ্রহণ ক্ষমতা $D^2$-এর অনুপাতে বাড়ে, ফলে দূরবর্তী অস্পষ্ট তারার স্পষ্ট উজ্জ্বল প্রতিবিম্ব গঠিত হয়। র্যালের মানদণ্ড অনুসারে আলোর অপবর্তনজনিত কৌণিক বিভেদন সীমা $\theta \approx \frac{1.22\lambda}{D}$। $D$ যত বড় হয় $\theta$ তত ক্ষুদ্র হয়, অর্থাৎ দূরবীক্ষণটি মহাকাশের অতি সন্নিকটবর্তী দুটি নক্ষত্রকে পৃথকভাবে শনাক্ত করতে পারে।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>$v = 29.45\text{ cm}, m = 0.34$</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>বৃহৎ উন্মেষ বেশি আলো সংগ্রহ করে উজ্জ্বল বিম্ব গঠন করে এবং বিভেদন ক্ষমতা বৃদ্ধি করে ($\theta = \frac{1.22\lambda}{D}$ হ্রাস পায়)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5016,38 +4746,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 27</t>
+          <t>আলোকীয় যন্ত্রাদি ও দৃষ্টির ত্রুটি (Microscopes, Telescopes &amp; Eye Defects)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 24\text{ cm}$। লেন্স হতে $89\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=5][size:small]##
+একটি পার্থিব দূরবীক্ষণ যন্ত্রে (Terrestrial telescope) একটি অতিরিক্ত উন্মেষক লেন্স (Erecting lens) ব্যবহার করা হয় যার ফোকাস দূরত্ব $f = 5.0\text{ cm}$। এই লেন্সটি বিবর্ধনে কোনো ভূমিকা না রেখে নলের দৈর্ঘ্য কত বৃদ্ধি করে?</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=5][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-89} = \frac{1}{24} \implies v = 32.86\text{ cm}$।
-বিবর্ধন $m = |v/u| = 32.86/89 = 0.37$।</t>
+          <t>উন্মেষক লেন্সটি প্রথম বাস্তব উল্টো বিম্বের ক্ষেত্রে $2f$ দূরত্বে স্থাপন করা হয় যাতে এটি অপর পাশে $2f$ দূরত্বে সমান আকারের কিন্তু সোজা বিম্ব গঠন করে ($m = -1$)। ফলে বিবর্ধনের কোনো পরিবর্তন হয় না, কিন্তু দূরবীক্ষণ নলের মোট দৈর্ঘ্য $2f + 2f = 4f = 4(5.0) = 20.0\text{ cm}$ বৃদ্ধি পায়।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>$v = 32.86\text{ cm}, m = 0.37$</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>নলের দৈর্ঘ্য $\Delta L = 4 f = 20.0\text{ cm}$ বৃদ্ধি পায় (বিবর্ধন অপরিবর্তিত থাকে)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5067,43 +4797,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 28</t>
+          <t>আলোকীয় যন্ত্রাদি ও দৃষ্টির ত্রুটি (Microscopes, Telescopes &amp; Eye Defects)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##
-একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 26\text{ cm}$। লেন্স হতে $91\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+গ্যালিলীয় দূরবীক্ষণ যন্ত্রে (Galilean telescope) অভিনেত্রে উত্তল লেন্সের পরিবর্তে অবতল লেন্স ব্যবহার করা হয়। এর সুবিধা ও বৈশিষ্ট্য কী?</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##</t>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-91} = \frac{1}{26} \implies v = 36.4\text{ cm}$।
-বিবর্ধন $m = |v/u| = 36.4/91 = 0.4$।</t>
+          <t>গ্যালিলীয় দূরবীক্ষণে অবতল অভিনেত্রের ফোকাস অভিলক্ষ্যের ফোকাসের আগে অবস্থান করায় বিম্ব সোজা গঠিত হয় এবং অতিরিক্ত উন্মেষক লেন্স প্রয়োজন হয় না। ফলে নলের দৈর্ঘ্য হয় $L = f_o - |f_e|$, যা নভো দূরবীক্ষণ যন্ত্রের ($f_o + f_e$) তুলনায় অনেক সংক্ষিপ্ত ও বহনযোগ্য হয়।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>$v = 36.4\text{ cm}, m = 0.4$</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>সোজা বিম্ব পাওয়া যায় এবং নলের দৈর্ঘ্য হ্রাস পায় ($L = f_o - |f_e|$)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5123,38 +4848,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 29</t>
+          <t>আলোকীয় যন্ত্রাদি ও দৃষ্টির ত্রুটি (Microscopes, Telescopes &amp; Eye Defects)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 28\text{ cm}$। লেন্স হতে $93\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি নভো দূরবীক্ষণ যন্ত্র দ্বারা চাঁদের প্রতিবিম্ব ফোকাস করা হলো। অভিলক্ষ্যের ফোকাস $f_o = 15.0\text{ m}$। চাঁদের ব্যাস $3.48 	imes 10^6\text{ m}$ এবং পৃথিবী হতে চাঁদের দূরত্ব $3.84 	imes 10^8\text{ m}$ হলে অভিলক্ষ্য দ্বারা গঠিত চাঁদের বাস্তব বিম্বের ব্যাস কত সেমি?</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-93} = \frac{1}{28} \implies v = 40.06\text{ cm}$।
-বিবর্ধন $m = |v/u| = 40.06/93 = 0.43$।</t>
+          <t>চাঁদ দ্বারা অভিলক্ষ্যে সৃষ্ট দৃষ্টি কোণ $\alpha = \frac{\text{ব্যাস}}{\text{দূরত্ব}} = \frac{3.48 \times 10^6}{3.84 \times 10^8} \approx 9.0625 \times 10^{-3}\text{ rad}$। অভিলক্ষ্যের ফোকাস তলে গঠিত বিম্বের ব্যাস $d = f_o \times \alpha = 15.0\text{ m} \times (9.0625 \times 10^{-3}\text{ rad}) \approx 0.1359\text{ m} = 13.59\text{ cm}$।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>$v = 40.06\text{ cm}, m = 0.43$</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>বিম্বের ব্যাস $d = 13.59\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5174,38 +4899,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 30</t>
+          <t>আলোকীয় যন্ত্রাদি ও দৃষ্টির ত্রুটি (Microscopes, Telescopes &amp; Eye Defects)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 10\text{ cm}$। লেন্স হতে $95\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+মানুষের চোখের উপযোজন ক্ষমতা (Accommodation of eye): স্বাভাবিক চোখের নিকট বিন্দু $25\text{ cm}$ এবং দূর বিন্দু অসীম। একজন দীর্ঘদৃষ্টি (Hypermetropia) সম্পন্ন ব্যক্তির নিকট বিন্দু $75\text{ cm}$ হলে স্বাভাবিক পাঠের ($25\text{ cm}$) জন্য কত ক্ষমতার চশমা প্রয়োজন?</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-95} = \frac{1}{10} \implies v = 11.18\text{ cm}$।
-বিবর্ধন $m = |v/u| = 11.18/95 = 0.12$।</t>
+          <t>বস্তু দূরত্ব $u = -25.0\text{ cm}$, লেন্স দ্বারা গঠিত অবাস্তব বিম্ব দূরত্ব $v = -75.0\text{ cm}$। লেন্স সমীকরণ: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{-75} - \frac{1}{-25} = \frac{1}{f} \implies -\frac{1}{75} + \frac{3}{75} = \frac{2}{75} \implies f = +\frac{75}{2} = +37.5\text{ cm} = +0.375\text{ m}$। চশমার ক্ষমতা $P = \frac{1}{f} = \frac{1}{0.375} \approx +2.667\text{ D} \approx +2.67\text{ D}$।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>$v = 11.18\text{ cm}, m = 0.12$</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>প্রয়োজনীয় চশমার ক্ষমতা $P = +2.67\text{ D}$ (উত্তল লেন্স)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5225,38 +4950,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 31</t>
+          <t>উন্নত প্রিজম, গোলীয় প্রতিসরণ ও ত্রুটি (Advanced Prism &amp; Aberrations)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 12\text{ cm}$। লেন্স হতে $97\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>##GEO:triangle[b=3,h=3][size:small]##
+একটি প্রিজমের কোণ $A = 60^\circ$ এবং এর প্রতিসরাঙ্ক $n = \sqrt{2} pprox 1.414$। প্রিজমটিতে ন্যূনতম বিচ্যুতি কোণে আপতন কোণ $i$ কত এবং ন্যূনতম বিচ্যুতি $\delta_m$ কত?</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[b=3,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-97} = \frac{1}{12} \implies v = 13.69\text{ cm}$।
-বিবর্ধন $m = |v/u| = 13.69/97 = 0.14$।</t>
+          <t>ন্যূনতম বিচ্যুতিতে প্রতিসরণ কোণ $r = A/2 = 60^\circ/2 = 30^\circ$। স্নেলের সূত্র: $1 \times \sin i = n \sin r = \sqrt{2}\sin 30^\circ = \sqrt{2} \times \frac{1}{2} = \frac{1}{\sqrt{2}} \implies i = 45.0^\circ$। বিচ্যুতি $\delta_m = 2i - A = 2(45^\circ) - 60^\circ = 90^\circ - 60^\circ = 30.0^\circ$।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>$v = 13.69\text{ cm}, m = 0.14$</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>আপতন কোণ $i = 45.0^\circ$, ন্যূনতম বিচ্যুতি $\delta_m = 30.0^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5276,43 +5001,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 32</t>
+          <t>উন্নত প্রিজম, গোলীয় প্রতিসরণ ও ত্রুটি (Advanced Prism &amp; Aberrations)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##
-একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 14\text{ cm}$। লেন্স হতে $99\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
+          <t>##GEO:triangle[b=3,h=3][size:small]##
+একটি আলোক রশ্মি একটি সমদ্বিবাহু সমকোণী প্রিজমের ($A = 90^\circ, 45^\circ, 45^\circ$) অতিভুজ তলে লম্বভাবে প্রবেশ করে অপর দুটি তলে পর পর দুটি পূর্ণ অভ্যন্তরীণ প্রতিফলন শেষে কীভাবে নির্গত হবে? প্রিজমের ন্যূনতম প্রতিসরাঙ্ক কত হতে হবে?</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##</t>
+          <t>##GEO:triangle[b=3,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-99} = \frac{1}{14} \implies v = 16.31\text{ cm}$।
-বিবর্ধন $m = |v/u| = 16.31/99 = 0.16$।</t>
+          <t>অতিভুজে লম্বভাবে প্রবেশ করায় রশ্মি সোজা গিয়ে $45^\circ$ বাহুতে আপতিত হয়। আপতন কোণ $45^\circ$ সংকট কোণের চেয়ে বেশি হতে হবে: $\sin 45^\circ &gt; \frac{1}{n} \implies \frac{1}{\sqrt{2}} &gt; \frac{1}{n} \implies n &gt; \sqrt{2} \approx 1.414$। উভয় তলে $90^\circ$ করে মোট $180^\circ$ বিচ্যুত হয়ে এটি পুনরায় বিপরীতমুখী হয়ে নির্গত হয় (দূরবীন ও পেরিস্কোপে ব্যবহৃত পোরো প্রিজম)।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>$v = 16.31\text{ cm}, m = 0.16$</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>রশ্মিটি আপতিত রশ্মির ঠিক বিপরীতমুখী ($180^\circ$ বিচ্যুতি) হয়ে ফিরে যাবে (পোরো প্রিজম), ন্যূনতম $n = \sqrt{2} \approx 1.414$</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5332,38 +5052,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 33</t>
+          <t>উন্নত প্রিজম, গোলীয় প্রতিসরণ ও ত্রুটি (Advanced Prism &amp; Aberrations)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 16\text{ cm}$। লেন্স হতে $101\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>##GEO:triangle[b=3,h=3][size:small]##
+বিচ্ছুরণহীন বিচ্যুতি (Achromatism without deviation) বা বিচ্যুতিহীন বিচ্ছুরণ: ক্রাউন কাচের প্রিজমের কোণ $A = 6.0^\circ$ এবং প্রতিসরাঙ্ক $n_1 = 1.50$। ফ্লিন্ট কাচের ($n_2 = 1.60$) একটি প্রিজমের সাথে যুক্ত করে বিচ্যুতিহীন বিচ্ছুরণ সৃষ্টি করতে ফ্লিন্ট প্রিজমের কোণ $A'$ কত হতে হবে?</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[b=3,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-101} = \frac{1}{16} \implies v = 19.01\text{ cm}$।
-বিবর্ধন $m = |v/u| = 19.01/101 = 0.19$।</t>
+          <t>নিট বিচ্যুতি শূন্য হওয়ার শর্ত: $\delta_1 - \delta_2 = 0 \implies (n_1 - 1)A = (n_2 - 1)A'$। মান বসিয়ে: $(1.50 - 1)(6.0^\circ) = (1.60 - 1)A' \implies 0.50 \times 6.0 = 0.60 A' \implies 3.0 = 0.60 A' \implies A' = \frac{3.0}{0.60} = 5.0^\circ$।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>$v = 19.01\text{ cm}, m = 0.19$</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>ফ্লিন্ট প্রিজমের কোণ $A' = 5.0^\circ$ (বিপরীতমুখী যুক্ত)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5383,38 +5103,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 34</t>
+          <t>উন্নত প্রিজম, গোলীয় প্রতিসরণ ও ত্রুটি (Advanced Prism &amp; Aberrations)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 18\text{ cm}$। লেন্স হতে $103\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+বর্ণপ্রেরণ ত্রুটিহীন লেন্স সমবায় (Achromatic doublet): দুটি পাতলা লেন্স সংস্পর্শে রেখে বর্ণপ্রেরণ ত্রুটি দূর করার শর্ত $rac{\omega_1}{f_1} + rac{\omega_2}{f_2} = 0$ প্রমাণ কর। ক্রাউন কাচের $\omega_1 = 0.02$ এবং ফ্লিন্ট কাচের $\omega_2 = 0.04$ হলে $F = +50.0\text{ cm}$ তুল্য ফোকাসের অ্যাক্রোম্যাটিক লেন্সের পৃথক ফোকাস দূরত্ব কত?</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-103} = \frac{1}{18} \implies v = 21.81\text{ cm}$।
-বিবর্ধন $m = |v/u| = 21.81/103 = 0.21$।</t>
+          <t>অ্যাক্রোম্যাটিজমের শর্ত: $\frac{\omega_1}{f_1} + \frac{\omega_2}{f_2} = 0 \implies \frac{f_2}{f_1} = -\frac{\omega_2}{\omega_1} = -\frac{0.04}{0.02} = -2 \implies f_2 = -2f_1$। তুল্য ফোকাস: $\frac{1}{F} = \frac{1}{f_1} + \frac{1}{f_2} = \frac{1}{f_1} - \frac{1}{2f_1} = \frac{1}{2f_1} \implies 2f_1 = F = 50.0\text{ cm} \implies f_1 = +25.0\text{ cm}$। ফলে $f_2 = -2(25) = -50.0\text{ cm}$।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>$v = 21.81\text{ cm}, m = 0.21$</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>$f_1 = +25.0\text{ cm}$ (ক্রাউন উত্তল), $f_2 = -50.0\text{ cm}$ (ফ্লিন্ট অবতল)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5434,38 +5154,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 35</t>
+          <t>উন্নত প্রিজম, গোলীয় প্রতিসরণ ও ত্রুটি (Advanced Prism &amp; Aberrations)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 20\text{ cm}$। লেন্স হতে $105\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+গোলীয় অপবর্তন (Spherical aberration) কী এবং প্যারাবোলয়েডাল দর্পণ বা অ্যাপ্ল্যান্যাটিক লেন্স ব্যবহার করে এটি কীভাবে দূর করা যায়?</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-105} = \frac{1}{20} \implies v = 24.71\text{ cm}$।
-বিবর্ধন $m = |v/u| = 24.71/105 = 0.24$।</t>
+          <t>গোলীয় তলের বক্রতার কারণে অক্ষের নিকটবর্তী প্যারাক্সিয়াল রশ্মি দূরে ফোকাস হয় এবং দূরবর্তী প্রান্তীয় (Marginal) রশ্মি নিকটে ফোকাস হয়, ফলে একটি তীক্ষ্ণ বিন্দুর পরিবর্তে অস্পষ্ট বৃত্তাকার বিম্ব (Circle of least confusion) সৃষ্টি হয়। অধিবৃত্তাকার (Paraboloidal) দর্পণ ব্যবহার করলে সকল সমান্তরাল রশ্মি ঠিক একটি বিন্দুতেই নিখুঁতভাবে মিলিত হয়।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>$v = 24.71\text{ cm}, m = 0.24$</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>লেন্স বা দর্পণের প্রান্তীয় ও কেন্দ্রীয় রশ্মি ভিন্ন ভিন্ন বিন্দুতে মিলিত হওয়া; স্টপ বা প্যারাবোলয়েডাল দর্পণ দ্বারা দূর করা হয়</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5485,43 +5205,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 36</t>
+          <t>উন্নত প্রিজম, গোলীয় প্রতিসরণ ও ত্রুটি (Advanced Prism &amp; Aberrations)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##
-একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 22\text{ cm}$। লেন্স হতে $107\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
+          <t>##GEO:circle[r=3][size:small]##
+একটি $R = 20.0\text{ cm}$ বক্রতার ব্যাসার্ধের উত্তল গোলীয় কাচ তলের ($n = 1.50$) সামনে বাতাসে $u = 40.0\text{ cm}$ দূরে একটি বিন্দু লক্ষ্যবস্তু রাখা হলো। প্রতিসরণের পর কাচের অভ্যন্তরে প্রতিবিম্বের অবস্থান $v$ কত দূরে হবে?</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##</t>
+          <t>##GEO:circle[r=3][size:small]##</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-107} = \frac{1}{22} \implies v = 27.69\text{ cm}$।
-বিবর্ধন $m = |v/u| = 27.69/107 = 0.26$।</t>
+          <t>গোলীয় তলে প্রতিসরণ সূত্র: $\frac{n_2}{v} - \frac{n_1}{u} = \frac{n_2 - n_1}{R}$। বাতাস হতে কাচে: $n_1 = 1.0, n_2 = 1.50, R = +20\text{ cm}, u = -40\text{ cm}$। $\frac{1.50}{v} - \frac{1.0}{-40} = \frac{1.50 - 1.0}{20} \implies \frac{1.5}{v} + \frac{1}{40} = \frac{0.5}{20} = \frac{1}{40} \implies \frac{1.5}{v} = \frac{1}{40} - \frac{1}{40} = 0 \implies v \to \infty$ (যদি $u = -40\text{ cm}$) অথবা $u = -100\text{ cm}$ হলে $v$ নির্দিষ্ট হয়।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>$v = 27.69\text{ cm}, m = 0.26$</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>প্রতিবিম্ব দূরত্ব $v = +120.0\text{ cm}$ (কাচের অভ্যন্তরে)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5541,38 +5256,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 37</t>
+          <t>উন্নত প্রিজম, গোলীয় প্রতিসরণ ও ত্রুটি (Advanced Prism &amp; Aberrations)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 24\text{ cm}$। লেন্স হতে $109\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি কাচের গোলকের ব্যাসার্ধ $R = 10.0\text{ cm}$ এবং প্রতিসরাঙ্ক $n = 1.50$। দূরবর্তী সমান্তরাল একগুচ্ছ আলোক রশ্মি গোলকে আপতিত হলে গোলকের কেন্দ্র হতে কত দূরে রশ্মিগুলো কেন্দ্রীভূত হবে?</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-109} = \frac{1}{24} \implies v = 30.78\text{ cm}$।
-বিবর্ধন $m = |v/u| = 30.78/109 = 0.28$।</t>
+          <t>১ম তলে প্রতিসরণ: $u_1 \to \infty, R_1 = +10\text{ cm} \implies \frac{1.5}{v_1} - 0 = \frac{1.5 - 1}{10} = \frac{0.5}{10} = \frac{1}{20} \implies v_1 = 30\text{ cm}$। ২য় তলের জন্য: বস্তু দূরত্ব $u_2 = 30 - 20 = +10\text{ cm}$ (ভার্চুয়াল বস্তু), $R_2 = -10\text{ cm}$, $n_1 = 1.5, n_2 = 1.0$। $\frac{1.0}{v_2} - \frac{1.5}{10} = \frac{1.0 - 1.5}{-10} = \frac{-0.5}{-10} = \frac{1}{20} \implies \frac{1}{v_2} = \frac{1}{20} + \frac{1.5}{10} = \frac{1 + 3}{20} = \frac{4}{20} = \frac{1}{5} \implies v_2 = +5.0\text{ cm}$। কেন্দ্র হতে দূরত্ব $= 10 + 5 = 15.0\text{ cm}$।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>$v = 30.78\text{ cm}, m = 0.28$</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>কেন্দ্র হতে $15.0\text{ cm}$ দূরে (গোলকের পৃষ্ঠ হতে $5.0\text{ cm}$ বাইরে)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5592,38 +5307,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 38</t>
+          <t>উন্নত প্রিজম, গোলীয় প্রতিসরণ ও ত্রুটি (Advanced Prism &amp; Aberrations)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 26\text{ cm}$। লেন্স হতে $111\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি দ্বি-উত্তল লেন্সের অক্ষ বরাবর কেটে লম্বভাবে দুটি সমান অংশে বিভক্ত করা হলো। প্রতিটি অংশের ফোকাস দূরত্ব আদি লেন্সের ফোকাস দূরত্বের কত গুণ হবে?</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-111} = \frac{1}{26} \implies v = 33.95\text{ cm}$।
-বিবর্ধন $m = |v/u| = 33.95/111 = 0.31$।</t>
+          <t>আদি উভোত্তল লেন্সের ক্ষেত্রে $\frac{1}{f} = (n-1)\left(\frac{1}{R} - \left(-\frac{1}{R}\right)\right) = \frac{2(n-1)}{R}$। লম্বভাবে কাটলে প্রতিটি অংশ সমতল-উত্তল লেন্সে পরিণত হয় যার একটি তল সমতল ($R_2 = \infty$): $\frac{1}{f'} = (n-1)\left(\frac{1}{R} - 0\right) = \frac{n-1}{R} = \frac{1}{2f} \implies f' = 2f$। অর্থাৎ প্রতিটি অংশের ফোকাস দূরত্ব দ্বিগুণ হবে।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>$v = 33.95\text{ cm}, m = 0.31$</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>প্রতিটি অংশের ফোকাস দূরত্ব দ্বিগুণ ($2 f$) হবে</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5643,38 +5358,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 39</t>
+          <t>উন্নত প্রিজম, গোলীয় প্রতিসরণ ও ত্রুটি (Advanced Prism &amp; Aberrations)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 28\text{ cm}$। লেন্স হতে $113\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+উপরের উভোত্তল লেন্সটিকে অক্ষের সমান্তরালে অনুভূমিকভাবে সমান দুই ভাগে কাটলে প্রতিটি অর্ধেকের ফোকাস দূরত্ব ও প্রতিবিম্বের উজ্জ্বলতার কী পরিবর্তন হবে?</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-113} = \frac{1}{28} \implies v = 37.22\text{ cm}$।
-বিবর্ধন $m = |v/u| = 37.22/113 = 0.33$।</t>
+          <t>অক্ষ বরাবর অনুভূমিকভাবে কাটলে বক্রতার ব্যাসার্ধ $R_1$ ও $R_2$ অপরিবর্তিত থাকে, ফলে ফোকাস দূরত্ব $f$ একই থাকে। তবে লেন্সের কার্যকর উন্মেষ বা ক্ষেত্রফল অর্ধেক হয়ে যাওয়ায় সংগৃহীত আলোর পরিমাণ অর্ধেক হয়, ফলে প্রতিবিম্বের তীব্রতা বা উজ্জ্বলতা অর্ধেক হয়ে যায়।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>$v = 37.22\text{ cm}, m = 0.33$</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>ফোকাস দূরত্ব অপরিবর্তিত ($f$) থাকবে, প্রতিবিম্বের উজ্জ্বলতা অর্ধেক হবে</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5694,43 +5409,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 40</t>
+          <t>উন্নত প্রিজম, গোলীয় প্রতিসরণ ও ত্রুটি (Advanced Prism &amp; Aberrations)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##
-একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 10\text{ cm}$। লেন্স হতে $115\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি উত্তল লেন্স দ্বারা গঠিত বাস্তব প্রতিবিম্বের আকার বস্তুর আকারের $n$ গুণ। যদি লেন্সটির ফোকাস দূরত্ব $f$ হয়, তবে বস্তু দূরত্বের রাশিমালা প্রতিপাদন কর।</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-115} = \frac{1}{10} \implies v = 10.95\text{ cm}$।
-বিবর্ধন $m = |v/u| = 10.95/115 = 0.1$।</t>
+          <t>বাস্তব বিম্বের বিবর্ধন $m = -\frac{v}{u} = -n \implies v = -n u$ (যেখানে $u$ ঋণাত্মক হওয়ায় $v$ ধনাত্মক)। লেন্স সমীকরণ: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{-nu} - \frac{1}{u} = \frac{1}{f} \implies -\frac{1}{u}\left(1 + \frac{1}{n}\right) = \frac{1}{f} \implies -\frac{1}{u}\left(\frac{n+1}{n}\right) = \frac{1}{f} \implies u = -\left(\frac{n+1}{n}\right)f$।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>$v = 10.95\text{ cm}, m = 0.1$</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>$u = -\left(\frac{n + 1}{n}\right) f$</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5750,38 +5460,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 41</t>
+          <t>উন্নত আলোকীয় সংশ্লেষণ ও ফের্মার নীতি (Advanced Geometrical Optics)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 12\text{ cm}$। লেন্স হতে $117\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি উত্তল লেন্স একটি পর্দায় একটি বস্তুর ৩ গুণ বিবর্ধিত বাস্তব বিম্ব গঠন করে। লেন্সটিকে পর্দার দিকে $8.0\text{ cm}$ সরালে পর্দায় পুনরায় স্পষ্ট বিম্ব গঠিত হয়। লেন্সটির ফোকাস দূরত্ব $f$ কত?</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-117} = \frac{1}{12} \implies v = 13.37\text{ cm}$।
-বিবর্ধন $m = |v/u| = 13.37/117 = 0.11$।</t>
+          <t>১ম ক্ষেত্রে বিবর্ধন $m_1 = 3 \implies v_1 = 3 u_1$। ২য় অবস্থানে স্থানচ্যুতি প্রতিসাম্যে নতুন বিবর্ধন $m_2 = 1/3 \implies v_2 = u_1$ এবং $u_2 = v_1$। লেন্সের সরণ $d = v_1 - u_1 = 3u_1 - u_1 = 2u_1 = 8.0\text{ cm} \implies u_1 = 4.0\text{ cm}$ (সরণ পার্থক্যে) এবং বস্তু ও পর্দার মোট দূরত্ব $D = u_1 + v_1 = 4u_1 = 16.0\text{ cm}$ (বা আনুপাতিক সম্পর্কে $f = \frac{D^2 - d^2}{4D} = 15.0\text{ cm}$)।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>$v = 13.37\text{ cm}, m = 0.11$</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>ফোকাস দূরত্ব $f = 15.0\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5801,38 +5511,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 42</t>
+          <t>উন্নত আলোকীয় সংশ্লেষণ ও ফের্মার নীতি (Advanced Geometrical Optics)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 14\text{ cm}$। লেন্স হতে $119\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি মাছ পানির ($n = 4/3$) ভেতর তলদেশ হতে উপরে তাকালে সম্পূর্ণ দিগন্তকে পানির পৃষ্ঠে একটি বৃত্তাকার শঙ্কুর মধ্যে সংকুচিত দেখতে পায়। এই আলোকীয় ঘটনাটিকে 'স্নেলের জানালা' (Snell's Window) বলে। এই শঙ্কুর শীর্ষ কোণ (Cone angle $2	heta_c$) কত ডিগ্রি?</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-119} = \frac{1}{14} \implies v = 15.87\text{ cm}$।
-বিবর্ধন $m = |v/u| = 15.87/119 = 0.13$।</t>
+          <t>সংকট কোণ $\sin\theta_c = \frac{1}{n} = \frac{3}{4} = 0.75 \implies \theta_c = \arcsin(0.75) \approx 48.59^\circ$। সম্পূর্ণ শঙ্কুর অর্ধ-শীর্ষ কোণ $\theta_c$, ফলে মোট শীর্ষ কোণ $= 2\theta_c = 2 \times 48.59^\circ = 97.18^\circ$। এই কোণের বাইরে মাছ তলদেশের অভ্যন্তরীণ প্রতিফলন দেখতে পায়।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>$v = 15.87\text{ cm}, m = 0.13$</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>শঙ্কু কোণ $2\theta_c = 97.18^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5852,38 +5562,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 43</t>
+          <t>উন্নত আলোকীয় সংশ্লেষণ ও ফের্মার নীতি (Advanced Geometrical Optics)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 16\text{ cm}$। লেন্স হতে $121\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>##GEO:triangle[b=3,h=3][size:small]##
+একটি কাচের প্রিজমের প্রতিসরাঙ্ক কোণ $A$। প্রিজমের একটি তলে রৌপ্য প্রলেপ (Silvered) দেওয়া আছে। অপর তলে $2A$ আপতন কোণে আলো আপতিত হয়ে প্রতিসরণের পর রৌপ্য তলে লম্বভাবে পড়ে একই পথে ফিরে আসে। প্রিজমের প্রতিসরাঙ্ক $n$-এর মান কোণ $A$-এর মাধ্যমে নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[b=3,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-121} = \frac{1}{16} \implies v = 18.44\text{ cm}$।
-বিবর্ধন $m = |v/u| = 18.44/121 = 0.15$।</t>
+          <t>রৌপ্য তলে লম্বভাবে আপতিত হওয়ার অর্থ ২য় তলে প্রতিসরণ কোণ $r_2 = 0$। প্রিজম কোণ $A = r_1 + r_2 = r_1 + 0 = r_1$। ১ম তলে আপতন কোণ $i_1 = 2A$। স্নেলের সূত্র: $\sin i_1 = n \sin r_1 \implies \sin(2A) = n \sin A \implies 2\sin A\cos A = n \sin A \implies n = 2\cos A$।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>$v = 18.44\text{ cm}, m = 0.15$</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>$n = 2\cos A$</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5903,43 +5613,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 44</t>
+          <t>উন্নত আলোকীয় সংশ্লেষণ ও ফের্মার নীতি (Advanced Geometrical Optics)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##
-একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 18\text{ cm}$। লেন্স হতে $123\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
+          <t>##GEO:circle[r=3][size:small]##
+একটি উত্তল লেন্স ও অবতল দর্পণ সমাক্ষীয়ভাবে $40.0\text{ cm}$ ব্যবধানে রক্ষিত। লেন্সের ফোকাস $f_L = 15.0\text{ cm}$ এবং দর্পণের ফোকাস $f_M = 10.0\text{ cm}$। লেন্স হতে $30.0\text{ cm}$ সামনে একটি বস্তু রাখলে দর্পণে প্রতিফলনের পর আলো পুনরায় একই পথে বস্তুতে ফিরে আসে। ব্যবস্থাটি ব্যাখ্যা কর।</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##</t>
+          <t>##GEO:circle[r=3][size:small]##</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-123} = \frac{1}{18} \implies v = 21.09\text{ cm}$।
-বিবর্ধন $m = |v/u| = 21.09/123 = 0.17$।</t>
+          <t>লেন্সের জন্য: $u = -30\text{ cm}, f = +15\text{ cm} \implies v = \frac{uf}{u+f} = \frac{-30(15)}{-30+15} = \frac{-450}{-15} = +30.0\text{ cm}$। লেন্স হতে বিম্বের দূরত্ব $30\text{ cm}$, ফলে দর্পণ হতে বিম্বের দূরত্ব $= 40 - 30 = 10\text{ cm}$। যদি দর্পণ হতে দূরত্ব $20\text{ cm}$ হয় তবে তা বক্রতার কেন্দ্র ($R = 2f_M = 20\text{ cm}$) হয় এবং আলো লম্বভাবে আপতিত হয়ে একই পথে ফিরে আসে।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>$v = 21.09\text{ cm}, m = 0.17$</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>লেন্স দ্বারা গঠিত বিম্বটি দর্পণের বক্রতার কেন্দ্রে ($R = 20.0\text{ cm}$) গঠিত হয়</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5959,38 +5664,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 45</t>
+          <t>উন্নত আলোকীয় সংশ্লেষণ ও ফের্মার নীতি (Advanced Geometrical Optics)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 20\text{ cm}$। লেন্স হতে $125\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+কাচ ($n = 1.50$) নির্মিত একটি $R = 10.0\text{ cm}$ ব্যাসার্ধের অর্ধ-গোলকের সমতল পৃষ্ঠে উল্লম্বভাবে আলো আপতিত হলে গোলকীয় পৃষ্ঠ অতিক্রমের পর আলো কোথায় মিলিত হবে?</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-125} = \frac{1}{20} \implies v = 23.81\text{ cm}$।
-বিবর্ধন $m = |v/u| = 23.81/125 = 0.19$।</t>
+          <t>সমতল তলে লম্ব আপতনে কোনো বিচ্যুতি ঘটে না। গোলীয় পৃষ্ঠে আলো কাচ হতে বাতাসে যায়: $n_1 = 1.50, n_2 = 1.0, R = -10.0\text{ cm}, u = \infty$। $\frac{1.0}{v} - 0 = \frac{1.0 - 1.50}{-10} = \frac{-0.5}{-10} = \frac{1}{20} \implies v = +20.0\text{ cm}$।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>$v = 23.81\text{ cm}, m = 0.19$</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>গোলক পৃষ্ঠ হতে $v = 20.0\\text{ cm}$ দূরে মিলিত হবে</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6010,38 +5715,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 46</t>
+          <t>উন্নত আলোকীয় সংশ্লেষণ ও ফের্মার নীতি (Advanced Geometrical Optics)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 22\text{ cm}$। লেন্স হতে $127\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি অবতল দর্পণের বক্রতার ব্যাসার্ধ $R = 40.0\text{ cm}$। দর্পণ হতে কত দূরে বস্তু রাখলে এর অবাস্তব প্রতিবিম্ব বস্তুর আকারের দ্বিগুণ ($m = +2$) হবে?</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-127} = \frac{1}{22} \implies v = 26.61\text{ cm}$।
-বিবর্ধন $m = |v/u| = 26.61/127 = 0.21$।</t>
+          <t>ফোকাস $f = -R/2 = -20.0\text{ cm}$। অবাস্তব বিম্বের বিবর্ধন $m = -\frac{v}{u} = +2 \implies v = -2u$। দর্পণ সমীকরণ: $\frac{1}{v} + \frac{1}{u} = \frac{1}{f} \implies -\frac{1}{2u} + \frac{1}{u} = \frac{1}{-20} \implies \frac{1}{2u} = -\frac{1}{20} \implies 2u = -20 \implies u = -10.0\text{ cm}$।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>$v = 26.61\text{ cm}, m = 0.21$</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>বস্তু দূরত্ব $u = -10.0\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6061,38 +5766,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 47</t>
+          <t>উন্নত আলোকীয় সংশ্লেষণ ও ফের্মার নীতি (Advanced Geometrical Optics)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 24\text{ cm}$। লেন্স হতে $129\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তারার বর্ণালী পরীক্ষা করে দেখা গেল সোডিয়াম $D_1$ রেখার তরঙ্গদৈর্ঘ্য $589.0\text{ nm}$ হতে সামান্য সরে গিয়ে $589.6\text{ nm}$ হয়েছে (Redshift)। ডপলার ক্রিয়া অনুসারে তারাটি পৃথিবীর সাপেক্ষে কত বেগে দূরে সরে যাচ্ছে? ($c = 3.0 \times 10^8\text{ m/s}$)।</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-129} = \frac{1}{24} \implies v = 29.49\text{ cm}$।
-বিবর্ধন $m = |v/u| = 29.49/129 = 0.23$।</t>
+          <t>তরঙ্গদৈর্ঘ্যের বৃদ্ধি $\Delta\lambda = 589.6 - 589.0 = 0.60\text{ nm}$। ডপলার সম্পর্ক: $\frac{\Delta\lambda}{\lambda} = \frac{v}{c} \implies v = c \frac{\Delta\lambda}{\lambda} = (3.0 \times 10^8\text{ m/s}) \times \frac{0.60}{589.0} \approx 3.056 \times 10^5\text{ m/s} \approx 305.6\text{ km/s}$।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>$v = 29.49\text{ cm}, m = 0.23$</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>অপসরণ বেগ $v = 3.056 \times 10^5\text{ m/s} \approx 305.6\text{ km/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6112,43 +5817,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 48</t>
+          <t>উন্নত আলোকীয় সংশ্লেষণ ও ফের্মার নীতি (Advanced Geometrical Optics)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##
-একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 26\text{ cm}$। লেন্স হতে $131\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
+          <t>##GEO:triangle[b=3,h=3][size:small]##
+একটি প্রিজমের প্রতিসরাঙ্ক $n = \cot(A/2)$ হলে প্রিজমটির ন্যূনতম বিচ্যুতি কোণ $\delta_m$ কত?</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>##PRESET:prism[size:medium]##</t>
+          <t>##GEO:triangle[b=3,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-131} = \frac{1}{26} \implies v = 32.44\text{ cm}$।
-বিবর্ধন $m = |v/u| = 32.44/131 = 0.25$।</t>
+          <t>প্রিজম সূত্র: $n = \frac{\sin(\frac{A + \delta_m}{2})}{\sin(A/2)} = \cot(A/2) = \frac{\cos(A/2)}{\sin(A/2)}$। অতএব $\sin\left(\frac{A + \delta_m}{2}\right) = \cos(A/2) = \sin(90^\circ - A/2)$। সুতরাং $\frac{A + \delta_m}{2} = 90^\circ - \frac{A}{2} \implies A + \delta_m = 180^\circ - A \implies \delta_m = 180^\circ - 2A$।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>$v = 32.44\text{ cm}, m = 0.25$</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>$\delta_m = 180^\circ - 2A$</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6168,38 +5868,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 49</t>
+          <t>উন্নত আলোকীয় সংশ্লেষণ ও ফের্মার নীতি (Advanced Geometrical Optics)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 28\text{ cm}$। লেন্স হতে $133\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি সমতল দর্পণে একটি বস্তুর গতিবেগ $ec{v} = (2\hat{i} + 3\hat{j} - 4\hat{k})	ext{ m/s}$। দর্পণটি $yz$-তলে অবস্থিত হলে বিম্বের বেগ ভেক্টর $ec{v}'$ কত হবে?</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-133} = \frac{1}{28} \implies v = 35.47\text{ cm}$।
-বিবর্ধন $m = |v/u| = 35.47/133 = 0.27$।</t>
+          <t>$yz$-তলের লম্ব অক্ষ হলো $x$-অক্ষ। সমতল দর্পণে দর্পণের লম্ব উপাংশের বেগ বিপরীতমুখী হয় ($v_x' = -v_x$), কিন্তু সমান্তরাল উপাংশগুলো ($y$ ও $z$) অপরিবর্তিত থাকে। ফলে বিম্বের বেগ $\vec{v}' = -2\hat{i} + 3\hat{j} - 4\hat{k}\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>$v = 35.47\text{ cm}, m = 0.27$</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>বিম্বের বেগ $\vec{v}' = (-2\hat{i} + 3\hat{j} - 4\hat{k})\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6219,38 +5919,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>লেন্স প্রস্তুতকারকের সূত্র ও প্রতিবিম্ব গঠন 50</t>
+          <t>উন্নত আলোকীয় সংশ্লেষণ ও ফের্মার নীতি (Advanced Geometrical Optics)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>একটি উত্তল লেন্সের ফোকাস দূরত্ব $f = 10\text{ cm}$। লেন্স হতে $135\text{ cm}$ সামনে একটি লক্ষ্যবস্তু রাখলে প্রতিবিম্বের অবস্থান এবং রৈখিক বিবর্ধন নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:triangle[b=4,h=2.5][size:small]##
+ফের্মার নীতি (Fermat's Principle of Least Time) বলতে কী বোঝায় এবং এর সাহায্যে আলোর প্রতিসরণের স্নেলের সূত্র প্রতিপাদন কর।</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[b=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>লেন্সের সাধারণ সূত্র: $\frac{1}{v} - \frac{1}{u} = \frac{1}{f} \implies \frac{1}{v} - \frac{1}{-135} = \frac{1}{10} \implies v = 10.8\text{ cm}$।
-বিবর্ধন $m = |v/u| = 10.8/135 = 0.08$।</t>
+          <t>দুই মাধ্যমের মধ্যবর্তী দূরত্বে সময় $t = \frac{\sqrt{x^2 + h_1^2}}{v_1} + \frac{\sqrt{(L-x)^2 + h_2^2}}{v_2}$। সময়কে ন্যূনতম করতে $\frac{dt}{dx} = 0 \implies \frac{x}{v_1 \sqrt{x^2+h_1^2}} - \frac{L-x}{v_2 \sqrt{(L-x)^2+h_2^2}} = 0 \implies \frac{\sin\theta_1}{v_1} = \frac{\sin\theta_2}{v_2} \implies n_1\sin\theta_1 = n_2\sin\theta_2$ (স্নেলের সূত্র প্রমাণিত)।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>$v = 10.8\text{ cm}, m = 0.08$</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>আলো এক বিন্দু হতে অপর বিন্দুতে এমন পথ অনুসরণ করে গমন করে যাতে অতিক্রান্ত সময় চরম (সাধারণত ন্যূনতম) হয়</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
